--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44851</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45031-2023</t>
+          <t>A 45030-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3229,7 +3229,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3271,21 +3271,144 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>14</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3299,112 +3422,230 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>3.8</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>6</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>9</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>3</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3418,116 +3659,116 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 1479-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>4</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>14</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3541,273 +3782,32 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>10</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>20</v>
-      </c>
-      <c r="U24" t="n">
-        <v>20</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>13</v>
-      </c>
-      <c r="U25" t="n">
-        <v>11</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
         <v/>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 28351-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45818</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -3994,12 +3994,482 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>13</v>
+      </c>
+      <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>9</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
         <v>17</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4011,506 +4481,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>13</v>
-      </c>
-      <c r="U28" t="n">
-        <v>13</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>7</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
         <v/>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45730</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26143-2024</t>
+          <t>A 15171-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45467</v>
+        <v>44658</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>48</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5145,159 +5145,159 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Knottrig blåslav
 Vedticka</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15171-2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>44658</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>48</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Tretåig hackspett
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10525-2024</t>
+          <t>A 36564-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45366</v>
+        <v>46269</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,18 +5326,23 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>15.5</v>
+        <v>21.5</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
         <v>2</v>
       </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -5351,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5360,163 +5365,158 @@
         <v>3</v>
       </c>
       <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp
+Kolflarnlav
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 10525-2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>45366</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
         <v>4</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Spindelblomster
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 36564-2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>5</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp
-Kolflarnlav
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45324-2022</t>
+          <t>A 41375-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44841</v>
+        <v>45559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5545,20 +5545,25 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>23.2</v>
+        <v>5.9</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5570,167 +5575,162 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Brudsporre</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 45324-2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>44841</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Bergand
 Sångsvan</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 41375-2024</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>45559</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Brudsporre</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
         <v/>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46076</v>
+        <v>45034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5877,17 +5877,17 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>18.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5913,46 +5913,50 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5966,10 +5970,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45777</v>
+        <v>45079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5981,17 +5985,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6006,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6022,42 +6031,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6071,10 +6080,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6087,16 +6096,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>18.8</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6111,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6123,50 +6132,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6180,10 +6185,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45079</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6195,37 +6200,32 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6241,35 +6241,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45625</v>
+        <v>45583</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.2</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45467</v>
+        <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.2</v>
+        <v>11.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7245,14 +7245,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45530</v>
+        <v>44475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,8 +7264,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7308,7 +7313,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7322,10 +7327,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45153</v>
+        <v>45187</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7337,13 +7342,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>16.9</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7396,14 +7396,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45664</v>
+        <v>44833</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7415,13 +7415,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>24.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7464,7 +7459,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7494,7 +7489,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>43.6</v>
+        <v>23.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7537,7 +7532,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7551,10 +7546,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45455</v>
+        <v>45859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7566,13 +7561,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7615,7 +7605,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7625,14 +7615,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45832</v>
+        <v>45250</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7645,7 +7635,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7688,7 +7678,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7702,10 +7692,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45079</v>
+        <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7717,13 +7707,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>22.7</v>
+        <v>10</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7766,7 +7751,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7776,14 +7761,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44475</v>
+        <v>45905</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7795,13 +7780,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7844,7 +7824,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7858,10 +7838,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44732</v>
+        <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7873,13 +7853,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>39</v>
+        <v>12.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7922,7 +7897,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7936,10 +7911,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45859</v>
+        <v>45079</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7951,8 +7926,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>22.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7995,7 +7975,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8009,10 +7989,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45903</v>
+        <v>45832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8025,7 +8005,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8068,7 +8048,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8082,10 +8062,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45905</v>
+        <v>45730</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8098,7 +8078,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8141,7 +8121,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8155,10 +8135,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45905</v>
+        <v>45079</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8170,8 +8150,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8214,7 +8199,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8228,10 +8213,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45825</v>
+        <v>44732</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8245,11 +8230,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>23.7</v>
+        <v>39</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8309,7 +8294,7 @@
         <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8365,7 +8350,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46747-2025</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8379,10 +8364,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45926</v>
+        <v>45315</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8395,7 +8380,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>19.7</v>
+        <v>9.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8438,7 +8423,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 46747-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8448,14 +8433,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45636</v>
+        <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8467,13 +8452,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>19.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8516,7 +8496,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8530,10 +8510,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44735</v>
+        <v>45664</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8551,7 +8531,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8594,7 +8574,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8604,14 +8584,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>45825</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8625,11 +8605,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.5</v>
+        <v>23.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8672,7 +8652,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8682,14 +8662,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45079</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8703,11 +8683,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>6.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8750,7 +8730,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8764,10 +8744,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45649</v>
+        <v>45636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8781,11 +8761,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8828,7 +8808,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8842,10 +8822,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46104</v>
+        <v>45455</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8859,11 +8839,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>31.7</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8906,7 +8886,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8920,10 +8900,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45187</v>
+        <v>45079</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8935,8 +8915,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8979,7 +8964,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8993,10 +8978,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45845</v>
+        <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9008,8 +8993,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>31.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9052,7 +9042,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9066,10 +9056,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45034</v>
+        <v>44473</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9081,13 +9071,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>20.3</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9130,7 +9115,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9144,10 +9129,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44874</v>
+        <v>45845</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9160,7 +9145,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9203,7 +9188,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9217,10 +9202,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44473</v>
+        <v>45034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9232,8 +9217,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>20.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9276,7 +9266,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9290,10 +9280,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45993</v>
+        <v>46139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9306,7 +9296,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9349,7 +9339,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9363,10 +9353,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45999</v>
+        <v>46139</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9379,7 +9369,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>11.3</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9422,7 +9412,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9436,10 +9426,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9452,7 +9442,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9495,7 +9485,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9509,10 +9499,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45469</v>
+        <v>45999</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9525,7 +9515,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>11.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9568,7 +9558,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9582,10 +9572,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46139</v>
+        <v>45999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9598,7 +9588,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9641,7 +9631,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9655,10 +9645,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46139</v>
+        <v>44701</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9671,7 +9661,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>20.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9714,7 +9704,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9731,7 +9721,7 @@
         <v>46139</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9744,7 +9734,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9787,7 +9777,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9804,7 +9794,7 @@
         <v>45469</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9817,7 +9807,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9860,7 +9850,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9874,10 +9864,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45315</v>
+        <v>45469</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9890,7 +9880,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9933,7 +9923,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9947,10 +9937,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45463</v>
+        <v>44741</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9962,13 +9952,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>30.7</v>
+        <v>15.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10011,7 +9996,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10025,10 +10010,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10041,7 +10026,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.9</v>
+        <v>13.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10084,7 +10069,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10098,10 +10083,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45079</v>
+        <v>45825</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10115,11 +10100,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7</v>
+        <v>25.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10162,7 +10147,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10176,10 +10161,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44741</v>
+        <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10192,7 +10177,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>15.6</v>
+        <v>6.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10235,7 +10220,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10249,10 +10234,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45625</v>
+        <v>46162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10265,7 +10250,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10308,7 +10293,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10318,14 +10303,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45625</v>
+        <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10337,8 +10322,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10381,7 +10371,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10395,10 +10385,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45625</v>
+        <v>45614</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10411,7 +10401,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10454,7 +10444,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10468,10 +10458,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45625</v>
+        <v>45468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10484,7 +10474,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10527,7 +10517,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10541,10 +10531,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46162</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10557,7 +10547,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7.7</v>
+        <v>16.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10600,7 +10590,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10610,14 +10600,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45825</v>
+        <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10631,11 +10621,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>25.1</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10678,7 +10668,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10692,10 +10682,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46162</v>
+        <v>46198</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10707,8 +10697,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10751,7 +10746,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10765,10 +10760,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45730</v>
+        <v>46198</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10780,8 +10775,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10834,14 +10834,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44735</v>
+        <v>46197</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10855,11 +10855,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>14.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10902,7 +10902,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10912,14 +10912,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45468</v>
+        <v>46252</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10931,8 +10931,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10975,7 +10980,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10985,14 +10990,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45614</v>
+        <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11004,8 +11009,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11048,7 +11058,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11062,10 +11072,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46181</v>
+        <v>46198</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11077,8 +11087,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11121,7 +11136,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11131,14 +11146,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45183</v>
+        <v>46198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11156,7 +11171,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11199,7 +11214,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11213,10 +11228,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11230,11 +11245,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11277,7 +11292,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11291,10 +11306,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45281</v>
+        <v>46197</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11306,8 +11321,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>22.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11350,7 +11370,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11360,14 +11380,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45281</v>
+        <v>45183</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11379,8 +11399,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>13.4</v>
+        <v>5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11423,7 +11448,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11433,14 +11458,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46197</v>
+        <v>46266</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11454,11 +11479,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>14.2</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11501,7 +11526,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11515,10 +11540,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46198</v>
+        <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11530,13 +11555,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11579,7 +11599,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11593,10 +11613,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46198</v>
+        <v>46028</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11608,13 +11628,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11657,7 +11672,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11667,14 +11682,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45583</v>
+        <v>45649</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11686,8 +11701,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11730,7 +11750,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11740,14 +11760,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45250</v>
+        <v>46269</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11759,8 +11779,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>13.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11803,7 +11828,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11817,10 +11842,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46252</v>
+        <v>44735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11834,11 +11859,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11881,7 +11906,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11891,14 +11916,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46189</v>
+        <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11910,13 +11935,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11959,7 +11979,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11973,10 +11993,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46198</v>
+        <v>45463</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11994,7 +12014,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>13.3</v>
+        <v>30.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12037,7 +12057,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12047,14 +12067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46197</v>
+        <v>45467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12066,13 +12086,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>17.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12115,7 +12130,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12129,10 +12144,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12144,13 +12159,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>17.2</v>
+        <v>43.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12193,7 +12203,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12207,10 +12217,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46197</v>
+        <v>45730</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12222,13 +12232,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>22.9</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12271,7 +12276,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12285,10 +12290,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45621</v>
+        <v>45530</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12301,7 +12306,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>11.3</v>
+        <v>20.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12344,7 +12349,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12358,10 +12363,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44701</v>
+        <v>45153</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12373,8 +12378,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>20.3</v>
+        <v>16.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12417,7 +12427,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12427,14 +12437,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46266</v>
+        <v>45281</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12446,13 +12456,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12495,7 +12500,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12509,10 +12514,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46269</v>
+        <v>45625</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12524,13 +12529,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>13.9</v>
+        <v>11.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44830</v>
+        <v>45625</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12602,13 +12602,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12651,7 +12646,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12665,10 +12660,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46028</v>
+        <v>45625</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12681,7 +12676,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12724,7 +12719,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12734,14 +12729,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44479</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12754,7 +12749,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>19.8</v>
+        <v>4.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12797,7 +12792,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12811,10 +12806,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44833</v>
+        <v>44830</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12826,8 +12821,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>24.6</v>
+        <v>6.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12870,7 +12870,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12880,14 +12880,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44833</v>
+        <v>44479</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>23.2</v>
+        <v>19.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12960,7 +12960,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="n">
+        <v>169</v>
+      </c>
+      <c r="U5" t="n">
         <v>168</v>
-      </c>
-      <c r="U5" t="n">
-        <v>167</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1140,6 +1140,7 @@
 Kristallskinn
 Kötticka
 Rosenticka
+Rutspindling
 Rynkskinn
 Skrovellav
 Talltita
@@ -1219,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1360,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1506,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1647,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1792,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1929,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2201,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2341,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2471,7 +2472,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2599,7 +2600,7 @@
         <v>44851</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2726,7 +2727,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2856,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2981,7 +2982,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3105,7 +3106,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3213,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45030-2023</t>
+          <t>A 45031-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3229,7 +3230,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3247,19 +3248,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3271,21 +3272,140 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>11</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3299,116 +3419,234 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45031-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>8</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>16</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>14</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3422,230 +3660,112 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="D25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>20</v>
-      </c>
-      <c r="U23" t="n">
-        <v>20</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>13</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>11</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3659,155 +3779,36 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>16</v>
-      </c>
-      <c r="U25" t="n">
-        <v>14</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Sprickporing
-Vitskaftad svartspik
-Gammelgransskål
-Rosenticka
-Ullticka
-Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3831,7 +3832,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3931,7 +3932,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28351-2025</t>
+          <t>A 4544-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3945,10 +3946,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45818</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3961,16 +3962,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3985,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -3994,12 +3995,128 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tajgaskinn
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Ullticka
+Blodticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
         <v>13</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4011,112 +4128,112 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 45032-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>45190</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>6.3</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M29" t="n">
         <v>2</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>8</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>7</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4128,111 +4245,111 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48673-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>32.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -4244,116 +4361,116 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 1478-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>6.2</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4365,152 +4482,36 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 4544-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>17</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tajgaskinn
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Ullticka
-Blodticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
@@ -4534,7 +4535,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4649,7 +4650,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4758,7 +4759,7 @@
         <v>45079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4859,7 +4860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12403-2025</t>
+          <t>A 64803-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4873,10 +4874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4889,19 +4890,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>43</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4916,18 +4917,126 @@
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
       </c>
       <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Gullmurkling
+Lunglav
+Rosenticka
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 12403-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45730</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="n">
         <v>9</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>9</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -4935,151 +5044,43 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 64803-2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>43</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Gullmurkling
-Lunglav
-Rosenticka
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15171-2022</t>
+          <t>A 26143-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44658</v>
+        <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5109,10 +5110,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>48</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5145,159 +5146,159 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15171-2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>44658</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>48</v>
+      </c>
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Tretåig hackspett
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 26143-2024</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45467</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36564-2026</t>
+          <t>A 10525-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5311,10 +5312,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46269</v>
+        <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,22 +5327,17 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>21.5</v>
+        <v>15.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5356,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5365,151 +5361,156 @@
         <v>3</v>
       </c>
       <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 36564-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
         <v>5</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Blå taggsvamp
 Kolflarnlav
 Stuplav</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 10525-2024</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>45366</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
     </row>
@@ -5533,7 +5534,7 @@
         <v>45559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5644,7 +5645,7 @@
         <v>44841</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5754,7 +5755,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5847,7 +5848,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5861,10 +5862,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45034</v>
+        <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5877,10 +5878,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>18.8</v>
+        <v>10.6</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5917,46 +5918,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5970,10 +5967,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45079</v>
+        <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5985,13 +5982,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -6027,46 +6019,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6080,10 +6072,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6096,17 +6088,17 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>18.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
@@ -6120,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6132,46 +6124,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6185,10 +6181,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>45079</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6200,17 +6196,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6225,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6241,35 +6242,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
@@ -6293,7 +6294,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6366,7 +6367,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6439,7 +6440,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6512,7 +6513,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6585,7 +6586,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6663,7 +6664,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6736,7 +6737,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6809,7 +6810,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6887,7 +6888,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6961,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7016,7 +7017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7026,14 +7027,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45583</v>
+        <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7045,8 +7046,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7089,7 +7095,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7103,10 +7109,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7125,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>18.3</v>
+        <v>11.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7162,7 +7168,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7176,10 +7182,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7192,7 +7198,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7235,7 +7241,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7249,10 +7255,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44475</v>
+        <v>45183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7266,11 +7272,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7313,7 +7319,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7327,10 +7333,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45187</v>
+        <v>45467</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7343,7 +7349,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>17.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7386,7 +7392,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7400,10 +7406,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44833</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7416,7 +7422,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>24.6</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7459,7 +7465,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7469,14 +7475,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44833</v>
+        <v>45636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7488,8 +7494,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>23.2</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7532,7 +7543,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7546,10 +7557,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45859</v>
+        <v>45079</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7561,8 +7572,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7605,7 +7621,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7615,14 +7631,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45250</v>
+        <v>45859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7635,7 +7651,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7678,7 +7694,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7692,10 +7708,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45903</v>
+        <v>45530</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7708,7 +7724,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>20.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7751,7 +7767,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7765,10 +7781,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7781,7 +7797,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7824,7 +7840,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7841,7 +7857,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7854,7 +7870,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7897,7 +7913,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7911,10 +7927,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45079</v>
+        <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7926,13 +7942,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>22.7</v>
+        <v>12.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7975,7 +7986,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7985,14 +7996,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45832</v>
+        <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8004,8 +8015,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8048,7 +8064,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8062,10 +8078,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8078,7 +8094,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.9</v>
+        <v>43.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8121,7 +8137,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8135,10 +8151,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45079</v>
+        <v>45153</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8152,11 +8168,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>16.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8199,7 +8215,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8213,10 +8229,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44732</v>
+        <v>45281</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8228,13 +8244,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>39</v>
+        <v>13.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8277,7 +8288,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8291,10 +8302,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>46104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8306,8 +8317,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>31.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8350,7 +8366,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8364,10 +8380,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45315</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8380,7 +8396,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8440,7 +8456,7 @@
         <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8496,7 +8512,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8506,14 +8522,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45664</v>
+        <v>45455</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8527,11 +8543,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8574,7 +8590,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8584,14 +8600,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45825</v>
+        <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8605,11 +8621,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>23.7</v>
+        <v>6.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8652,7 +8668,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8666,10 +8682,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>44475</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8687,7 +8703,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8730,7 +8746,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8740,14 +8756,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45636</v>
+        <v>45469</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8759,13 +8775,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8808,7 +8819,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8822,10 +8833,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45455</v>
+        <v>46139</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8837,13 +8848,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8886,7 +8892,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8900,10 +8906,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45079</v>
+        <v>46139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8915,13 +8921,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8964,7 +8965,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8978,10 +8979,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8993,13 +8994,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>31.7</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9042,7 +9038,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9056,10 +9052,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44473</v>
+        <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9072,7 +9068,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9132,7 +9128,7 @@
         <v>45845</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9188,7 +9184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9202,10 +9198,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45034</v>
+        <v>45583</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9217,13 +9213,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>20.3</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9266,7 +9257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9276,14 +9267,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46139</v>
+        <v>45250</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9296,7 +9287,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9339,7 +9330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9353,10 +9344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46139</v>
+        <v>45034</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9368,8 +9359,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>20.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9412,7 +9408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9422,14 +9418,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45993</v>
+        <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9441,8 +9437,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9485,7 +9486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9499,10 +9500,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9515,7 +9516,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.3</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9558,7 +9559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9572,10 +9573,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45999</v>
+        <v>44741</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9588,7 +9589,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>15.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9631,7 +9632,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9641,14 +9642,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44701</v>
+        <v>45649</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9660,8 +9661,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>20.3</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9704,7 +9710,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9718,10 +9724,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46139</v>
+        <v>45999</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9734,7 +9740,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>11.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9777,7 +9783,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9791,10 +9797,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45469</v>
+        <v>45999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9807,7 +9813,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9850,7 +9856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9864,10 +9870,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45469</v>
+        <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9880,7 +9886,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9923,7 +9929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9937,10 +9943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44741</v>
+        <v>46162</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9953,7 +9959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>15.6</v>
+        <v>7.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9996,7 +10002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10010,10 +10016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45281</v>
+        <v>45825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10025,8 +10031,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>13.4</v>
+        <v>25.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10069,7 +10080,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10083,10 +10094,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45825</v>
+        <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10098,13 +10109,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>25.1</v>
+        <v>6.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10147,7 +10153,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10161,10 +10167,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46162</v>
+        <v>44874</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10177,7 +10183,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10220,7 +10226,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10234,10 +10240,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46162</v>
+        <v>44473</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10250,7 +10256,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10293,7 +10299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10303,14 +10309,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44735</v>
+        <v>45468</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10322,13 +10328,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10388,7 +10389,7 @@
         <v>45614</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10444,7 +10445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10458,10 +10459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45468</v>
+        <v>45730</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10474,7 +10475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10517,7 +10518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10531,10 +10532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>45079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10546,8 +10547,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>16.9</v>
+        <v>7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10590,7 +10596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10600,14 +10606,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10619,13 +10625,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>16.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10668,7 +10669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10678,14 +10679,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10699,11 +10700,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>18</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10746,7 +10747,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10760,10 +10761,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46198</v>
+        <v>45315</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10775,13 +10776,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>11.5</v>
+        <v>9.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10824,7 +10820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10838,10 +10834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46197</v>
+        <v>45463</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10859,7 +10855,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>14.2</v>
+        <v>30.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10902,7 +10898,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10912,14 +10908,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46252</v>
+        <v>46197</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10933,11 +10929,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>14.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10980,7 +10976,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10990,14 +10986,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11011,11 +11007,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>18</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11058,7 +11054,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11075,7 +11071,7 @@
         <v>46198</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11093,7 +11089,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>17.2</v>
+        <v>11.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11136,7 +11132,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11150,10 +11146,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46198</v>
+        <v>45621</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11165,13 +11161,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>13.3</v>
+        <v>11.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11214,7 +11205,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11224,14 +11215,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46197</v>
+        <v>45625</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11243,13 +11234,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11292,7 +11278,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11306,10 +11292,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46197</v>
+        <v>45625</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11321,13 +11307,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>22.9</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11370,7 +11351,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11384,10 +11365,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45183</v>
+        <v>46252</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11401,11 +11382,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11448,7 +11429,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11458,14 +11439,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46266</v>
+        <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11477,13 +11458,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>20.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11526,7 +11502,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11543,7 +11519,7 @@
         <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11556,7 +11532,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11599,7 +11575,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11613,10 +11589,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46028</v>
+        <v>45625</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11629,7 +11605,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11672,7 +11648,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11686,10 +11662,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45649</v>
+        <v>46189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11703,11 +11679,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11750,7 +11726,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11764,10 +11740,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46269</v>
+        <v>46198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11781,11 +11757,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11828,7 +11804,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11842,10 +11818,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44735</v>
+        <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11859,11 +11835,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11906,7 +11882,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11920,10 +11896,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44874</v>
+        <v>46198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11935,8 +11911,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>3.4</v>
+        <v>17.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11979,7 +11960,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11993,10 +11974,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45463</v>
+        <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12014,7 +11995,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12057,7 +12038,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12071,10 +12052,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45467</v>
+        <v>45730</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12087,7 +12068,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>17.2</v>
+        <v>4.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12130,7 +12111,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12140,14 +12121,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45281</v>
+        <v>46266</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12159,8 +12140,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>43.6</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12203,7 +12189,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12217,10 +12203,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45730</v>
+        <v>44830</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12232,8 +12218,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12276,7 +12267,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12290,10 +12281,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45530</v>
+        <v>46269</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12305,8 +12296,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>20.1</v>
+        <v>13.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12349,7 +12345,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12363,10 +12359,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45153</v>
+        <v>46028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12378,13 +12374,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12427,7 +12418,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12437,14 +12428,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45281</v>
+        <v>44479</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12457,7 +12448,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>19.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12500,7 +12491,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12514,10 +12505,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45625</v>
+        <v>44833</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12530,7 +12521,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11.2</v>
+        <v>24.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12573,7 +12564,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12587,10 +12578,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45625</v>
+        <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12603,7 +12594,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.1</v>
+        <v>23.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12646,7 +12637,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12660,10 +12651,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45625</v>
+        <v>45832</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12676,7 +12667,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12719,7 +12710,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12733,10 +12724,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12748,8 +12739,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>22.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12792,7 +12788,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12806,10 +12802,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44830</v>
+        <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12823,11 +12819,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.5</v>
+        <v>39</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12870,7 +12866,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12880,14 +12876,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44479</v>
+        <v>45825</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12899,8 +12895,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>19.8</v>
+        <v>23.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12960,7 +12961,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T5" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U5" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,6 @@
 Kristallskinn
 Kötticka
 Rosenticka
-Rutspindling
 Rynkskinn
 Skrovellav
 Talltita
@@ -1220,7 +1219,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1360,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1506,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1647,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1792,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1929,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2068,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2201,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2341,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2471,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2600,7 +2599,7 @@
         <v>44851</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2727,7 +2726,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2856,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2982,7 +2981,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3106,7 +3105,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3213,7 +3212,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45031-2023</t>
+          <t>A 45030-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3230,7 +3229,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3248,19 +3247,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3272,21 +3271,144 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>14</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3300,112 +3422,230 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>3.8</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>6</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>9</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>3</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3419,234 +3659,116 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="D25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>20</v>
-      </c>
-      <c r="U23" t="n">
-        <v>20</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>14</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3660,155 +3782,32 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>13</v>
-      </c>
-      <c r="U25" t="n">
-        <v>11</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
         <v/>
       </c>
     </row>
@@ -3832,7 +3831,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3932,7 +3931,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 28351-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3946,10 +3945,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45818</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3962,16 +3961,16 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3986,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -3995,12 +3994,361 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>13</v>
+      </c>
+      <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
         <v>17</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4012,228 +4360,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="D31" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
-        <v>13</v>
-      </c>
-      <c r="U28" t="n">
-        <v>13</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4245,243 +4481,6 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
@@ -4535,7 +4534,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4650,7 +4649,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4759,7 +4758,7 @@
         <v>45079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4877,7 +4876,7 @@
         <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4985,7 +4984,7 @@
         <v>45730</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5080,7 +5079,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26143-2024</t>
+          <t>A 15171-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5094,10 +5093,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45467</v>
+        <v>44658</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5110,10 +5109,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>48</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5146,152 +5145,152 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Knottrig blåslav
 Vedticka</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15171-2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>44658</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>48</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Tretåig hackspett
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
         <v/>
       </c>
     </row>
@@ -5315,7 +5314,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5422,7 +5421,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5534,7 +5533,7 @@
         <v>45559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5645,7 +5644,7 @@
         <v>44841</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5755,7 +5754,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5848,7 +5847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5862,10 +5861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45777</v>
+        <v>45034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5878,10 +5877,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10.6</v>
+        <v>18.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5918,42 +5917,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5967,10 +5970,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46076</v>
+        <v>45079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5982,8 +5985,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -6019,46 +6027,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6072,10 +6080,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6088,16 +6096,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>18.8</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6112,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6124,50 +6132,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6181,10 +6185,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45079</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6196,37 +6200,32 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6242,35 +6241,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
@@ -6294,7 +6293,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6367,7 +6366,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6440,7 +6439,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6513,7 +6512,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6586,7 +6585,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6664,7 +6663,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6737,7 +6736,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6810,7 +6809,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6888,7 +6887,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6961,7 +6960,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7017,7 +7016,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7027,14 +7026,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44735</v>
+        <v>45583</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7046,13 +7045,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7095,7 +7089,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7109,10 +7103,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45625</v>
+        <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,7 +7119,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.2</v>
+        <v>18.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7168,7 +7162,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7178,14 +7172,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45618</v>
+        <v>44475</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7197,8 +7191,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>18.3</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7241,7 +7240,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7251,14 +7250,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45183</v>
+        <v>45621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7270,13 +7269,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>11.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7319,7 +7313,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7333,10 +7327,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45467</v>
+        <v>45187</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7349,7 +7343,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>17.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7392,7 +7386,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7402,14 +7396,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>45250</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7422,7 +7416,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7465,7 +7459,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7475,14 +7469,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45636</v>
+        <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7494,13 +7488,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>24.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7543,7 +7532,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7557,10 +7546,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45079</v>
+        <v>44833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7572,13 +7561,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>29</v>
+        <v>23.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7638,7 +7622,7 @@
         <v>45859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7694,7 +7678,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7708,10 +7692,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45530</v>
+        <v>45315</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7724,7 +7708,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>20.1</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7767,7 +7751,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7781,10 +7765,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45903</v>
+        <v>45079</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7796,8 +7780,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>22.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7840,7 +7829,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7854,10 +7843,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7870,7 +7859,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7913,7 +7902,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7930,7 +7919,7 @@
         <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7943,7 +7932,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7986,7 +7975,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7996,14 +7985,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45664</v>
+        <v>45905</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8015,13 +8004,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>12.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8064,7 +8048,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8078,10 +8062,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45281</v>
+        <v>45832</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8094,7 +8078,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>43.6</v>
+        <v>4.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8137,7 +8121,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8147,14 +8131,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45153</v>
+        <v>45664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8168,11 +8152,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>16.9</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8215,7 +8199,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8229,10 +8213,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45281</v>
+        <v>44732</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8244,8 +8228,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>13.4</v>
+        <v>39</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8288,7 +8277,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8302,10 +8291,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46104</v>
+        <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8317,13 +8306,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>31.7</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8366,7 +8350,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 46747-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8380,10 +8364,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8396,7 +8380,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8439,7 +8423,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46747-2025</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8453,10 +8437,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45926</v>
+        <v>45455</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8468,8 +8452,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>19.7</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8512,7 +8501,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8526,10 +8515,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45455</v>
+        <v>45825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8543,11 +8532,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>23.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8607,7 +8596,7 @@
         <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8668,7 +8657,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8678,14 +8667,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44475</v>
+        <v>45730</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8697,13 +8686,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>7.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8746,7 +8730,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8760,10 +8744,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45469</v>
+        <v>45079</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8775,8 +8759,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8819,7 +8808,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8833,10 +8822,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46139</v>
+        <v>44473</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8849,7 +8838,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8892,7 +8881,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8906,10 +8895,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46139</v>
+        <v>45845</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8922,7 +8911,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8965,7 +8954,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8979,10 +8968,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46139</v>
+        <v>45034</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8994,8 +8983,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>20.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9038,7 +9032,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9048,14 +9042,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45469</v>
+        <v>45636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9067,8 +9061,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9111,7 +9110,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9125,10 +9124,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45845</v>
+        <v>44701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9141,7 +9140,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>20.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9184,7 +9183,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9198,10 +9197,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45583</v>
+        <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9214,7 +9213,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9257,7 +9256,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9267,14 +9266,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45250</v>
+        <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9287,7 +9286,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>11.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9330,7 +9329,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9344,10 +9343,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45034</v>
+        <v>45999</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9359,13 +9358,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>20.3</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9408,7 +9402,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9418,14 +9412,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44735</v>
+        <v>45079</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9443,7 +9437,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>29</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9486,7 +9480,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9500,10 +9494,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45993</v>
+        <v>46104</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9515,8 +9509,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>31.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9559,7 +9558,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9573,10 +9572,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44741</v>
+        <v>45281</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9589,7 +9588,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>15.6</v>
+        <v>13.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9632,7 +9631,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9646,10 +9645,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45649</v>
+        <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9667,7 +9666,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9710,7 +9709,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9724,10 +9723,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45999</v>
+        <v>46139</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9740,7 +9739,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9783,7 +9782,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9793,14 +9792,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45999</v>
+        <v>45183</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9810,6 +9809,11 @@
       <c r="G95" t="inlineStr">
         <is>
           <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -9856,7 +9860,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9870,10 +9874,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45187</v>
+        <v>46139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9886,7 +9890,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9929,7 +9933,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9943,10 +9947,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46162</v>
+        <v>45625</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9959,7 +9963,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10002,7 +10006,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10016,10 +10020,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45825</v>
+        <v>46139</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10031,13 +10035,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>25.1</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10080,7 +10079,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10090,14 +10089,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46162</v>
+        <v>45649</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10109,8 +10108,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10153,7 +10157,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10167,10 +10171,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44874</v>
+        <v>45469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10183,7 +10187,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10226,7 +10230,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10240,10 +10244,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44473</v>
+        <v>45469</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10256,7 +10260,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10299,7 +10303,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10309,14 +10313,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45468</v>
+        <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10328,8 +10332,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10372,7 +10381,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10386,10 +10395,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45614</v>
+        <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10402,7 +10411,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>15.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10445,7 +10454,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10459,10 +10468,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45730</v>
+        <v>45825</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10474,8 +10483,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>7.9</v>
+        <v>25.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10518,7 +10532,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10532,10 +10546,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45079</v>
+        <v>46162</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10547,13 +10561,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10596,7 +10605,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10610,10 +10619,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46181</v>
+        <v>44874</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10626,7 +10635,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>16.9</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10669,7 +10678,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10679,14 +10688,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46188</v>
+        <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10698,13 +10707,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10747,7 +10751,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10761,10 +10765,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45315</v>
+        <v>45463</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10776,8 +10780,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>9.1</v>
+        <v>30.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10820,7 +10829,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10834,10 +10843,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45463</v>
+        <v>45467</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10849,13 +10858,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>30.7</v>
+        <v>17.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10898,7 +10902,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10912,10 +10916,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46197</v>
+        <v>45281</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10927,13 +10931,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>43.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10976,7 +10975,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10990,10 +10989,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46198</v>
+        <v>45614</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11005,13 +11004,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11054,7 +11048,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11068,10 +11062,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46198</v>
+        <v>45468</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11083,13 +11077,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>11.5</v>
+        <v>6.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11132,7 +11121,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11146,10 +11135,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45621</v>
+        <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11162,7 +11151,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>11.3</v>
+        <v>16.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11205,7 +11194,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11215,14 +11204,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45625</v>
+        <v>46188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11234,8 +11223,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11278,7 +11272,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11292,10 +11286,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45625</v>
+        <v>45730</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11308,7 +11302,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11351,7 +11345,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11361,14 +11355,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46252</v>
+        <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11382,11 +11376,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>18</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11429,7 +11423,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11443,10 +11437,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44701</v>
+        <v>46198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11458,8 +11452,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>20.3</v>
+        <v>11.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11502,7 +11501,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11516,10 +11515,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45625</v>
+        <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11531,8 +11530,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>4.3</v>
+        <v>14.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11575,7 +11579,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11589,10 +11593,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45625</v>
+        <v>45530</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11605,7 +11609,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.5</v>
+        <v>20.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11648,7 +11652,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11662,10 +11666,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46189</v>
+        <v>46252</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11683,7 +11687,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11726,7 +11730,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11736,14 +11740,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46198</v>
+        <v>46189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11757,11 +11761,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>13.3</v>
+        <v>0.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11804,7 +11808,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11814,14 +11818,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46197</v>
+        <v>45153</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11835,11 +11839,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>16.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11899,7 +11903,7 @@
         <v>46198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11960,7 +11964,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11974,10 +11978,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11995,7 +11999,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>22.9</v>
+        <v>13.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12038,7 +12042,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12048,14 +12052,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45730</v>
+        <v>46197</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12067,8 +12071,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12111,7 +12120,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12121,14 +12130,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46266</v>
+        <v>46197</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12142,11 +12151,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>22.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12189,7 +12198,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12203,10 +12212,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44830</v>
+        <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12218,13 +12227,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12267,7 +12271,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12281,10 +12285,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46269</v>
+        <v>45625</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12296,13 +12300,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>13.9</v>
+        <v>11.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12345,7 +12344,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12355,14 +12354,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46028</v>
+        <v>46266</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12374,8 +12373,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12418,7 +12422,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12428,14 +12432,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44479</v>
+        <v>45625</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12448,7 +12452,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>19.8</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12491,7 +12495,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12505,10 +12509,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44833</v>
+        <v>46028</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12521,7 +12525,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>24.6</v>
+        <v>19.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12564,7 +12568,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12578,10 +12582,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44833</v>
+        <v>46269</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12593,8 +12597,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>23.2</v>
+        <v>13.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12637,7 +12646,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12651,10 +12660,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45832</v>
+        <v>45625</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12667,7 +12676,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12710,7 +12719,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12724,10 +12733,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45079</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12739,13 +12748,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>22.7</v>
+        <v>4.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12788,7 +12792,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12802,10 +12806,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44732</v>
+        <v>44830</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12819,11 +12823,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>39</v>
+        <v>6.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12866,7 +12870,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12876,14 +12880,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45825</v>
+        <v>44479</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12895,13 +12899,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>23.7</v>
+        <v>19.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12961,7 +12960,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="n">
+        <v>169</v>
+      </c>
+      <c r="U5" t="n">
         <v>168</v>
-      </c>
-      <c r="U5" t="n">
-        <v>167</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1140,6 +1140,7 @@
 Kristallskinn
 Kötticka
 Rosenticka
+Rutspindling
 Rynkskinn
 Skrovellav
 Talltita
@@ -1219,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1360,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1506,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1647,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1792,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1929,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2201,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2341,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2471,7 +2472,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2599,7 +2600,7 @@
         <v>44851</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2709,7 +2710,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64805-2023</t>
+          <t>A 64837-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2726,7 +2727,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2738,25 +2739,20 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>12.7</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2768,21 +2764,151 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>17</v>
       </c>
       <c r="T17" t="n">
+        <v>57</v>
+      </c>
+      <c r="U17" t="n">
+        <v>57</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Blanksvart spiklav
+Blågrå svartspik
+Dvärgbägarlav
+Gammelgransskål
+Knottrig blåslav
+Kolflarnlav
+Kortskaftad ärgspik
+Mörk kolflarnlav
+Talltagel
+Tretåig hackspett
+Vedflamlav
+Vedskivlav
+Spindelblomster
+Vedticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64837-2023 artfynd.xlsx", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64837-2023 karta.png", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64837-2023 georefererad karta.tif", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64837-2023 FSC-klagomål.docx", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64837-2023 FSC-klagomål mail.docx", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64837-2023 tillsynsbegäran.docx", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64837-2023 tillsynsbegäran mail.docx", "A 64837-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64837-2023 prioriterade fågelarter.docx", "A 64837-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 64805-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>17</v>
+      </c>
+      <c r="T18" t="n">
         <v>55</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>55</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -2803,161 +2929,36 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64805-2023 artfynd.xlsx", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64805-2023 karta.png", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64805-2023 georefererad karta.tif", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64805-2023 FSC-klagomål.docx", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64805-2023 FSC-klagomål mail.docx", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64805-2023 tillsynsbegäran.docx", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64805-2023 tillsynsbegäran mail.docx", "A 64805-2023")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64805-2023 prioriterade fågelarter.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 64837-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>12</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>14</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>17</v>
-      </c>
-      <c r="T18" t="n">
-        <v>57</v>
-      </c>
-      <c r="U18" t="n">
-        <v>57</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Blanksvart spiklav
-Blågrå svartspik
-Dvärgbägarlav
-Gammelgransskål
-Knottrig blåslav
-Kolflarnlav
-Kortskaftad ärgspik
-Mörk kolflarnlav
-Talltagel
-Tretåig hackspett
-Vedflamlav
-Vedskivlav
-Spindelblomster
-Vedticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64837-2023 artfynd.xlsx", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64837-2023 karta.png", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64837-2023 georefererad karta.tif", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64837-2023 FSC-klagomål.docx", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64837-2023 FSC-klagomål mail.docx", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64837-2023 tillsynsbegäran.docx", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64837-2023 tillsynsbegäran mail.docx", "A 64837-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64837-2023 prioriterade fågelarter.docx", "A 64837-2023")</f>
         <v/>
       </c>
     </row>
@@ -2981,7 +2982,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3105,7 +3106,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3213,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45030-2023</t>
+          <t>A 45031-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3229,7 +3230,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3247,19 +3248,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3271,21 +3272,259 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>14</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>11</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3299,230 +3538,234 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45031-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45190</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
-        <v>16</v>
-      </c>
-      <c r="U22" t="n">
-        <v>14</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
-Sprickporing
-Vitskaftad svartspik
+Ostticka
 Gammelgransskål
-Rosenticka
+Harticka
+Knottrig blåslav
+Tretåig hackspett
 Ullticka
 Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 45417-2024</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45576</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>11.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>10</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>20</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>20</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Dvärgbägarlav
@@ -3536,278 +3779,36 @@
 Vedtrappmossa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13</v>
-      </c>
-      <c r="U24" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>16</v>
-      </c>
-      <c r="U25" t="n">
-        <v>14</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Sprickporing
-Vitskaftad svartspik
-Gammelgransskål
-Rosenticka
-Ullticka
-Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3831,7 +3832,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3931,7 +3932,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28351-2025</t>
+          <t>A 4544-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3945,10 +3946,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45818</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3961,16 +3962,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3985,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -3994,12 +3995,486 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tajgaskinn
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Ullticka
+Blodticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>9</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
         <v>13</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U31" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4011,506 +4486,32 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>9</v>
-      </c>
-      <c r="U28" t="n">
-        <v>7</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 4544-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>17</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tajgaskinn
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Ullticka
-Blodticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
         <v/>
       </c>
     </row>
@@ -4534,7 +4535,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4649,7 +4650,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4758,7 +4759,7 @@
         <v>45079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4876,7 +4877,7 @@
         <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4984,7 +4985,7 @@
         <v>45730</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5079,7 +5080,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15171-2022</t>
+          <t>A 26143-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,10 +5094,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44658</v>
+        <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5109,10 +5110,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>48</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5145,152 +5146,152 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15171-2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>44658</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>48</v>
+      </c>
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Tretåig hackspett
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 26143-2024</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45467</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
@@ -5314,7 +5315,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5421,7 +5422,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5516,7 +5517,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41375-2024</t>
+          <t>A 45324-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5526,14 +5527,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45559</v>
+        <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5545,26 +5546,21 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>23.2</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -5575,162 +5571,167 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Bergand
+Sångsvan</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 41375-2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45559</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
         <v>4</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Brudsporre</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 45324-2022</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>44841</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Bergand
-Sångsvan</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
         <v/>
       </c>
     </row>
@@ -5754,7 +5755,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5847,7 +5848,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5861,10 +5862,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45034</v>
+        <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5877,16 +5878,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>18.8</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5901,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5913,50 +5914,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5970,10 +5967,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45079</v>
+        <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5985,37 +5982,32 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6.9</v>
+        <v>10.6</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6031,42 +6023,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6080,10 +6072,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6096,17 +6088,17 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>18.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
@@ -6120,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6132,46 +6124,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6185,10 +6181,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>45079</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6200,17 +6196,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6225,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6241,35 +6242,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
@@ -6293,7 +6294,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6366,7 +6367,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6439,7 +6440,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6512,7 +6513,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6585,7 +6586,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6663,7 +6664,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6736,7 +6737,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6809,7 +6810,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6887,7 +6888,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6961,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7016,7 +7017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7030,10 +7031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45583</v>
+        <v>45625</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7046,7 +7047,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>11.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7106,7 +7107,7 @@
         <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7162,7 +7163,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7172,14 +7173,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44475</v>
+        <v>45467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7191,13 +7192,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>17.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7240,7 +7236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7254,10 +7250,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45621</v>
+        <v>45530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7270,7 +7266,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.3</v>
+        <v>20.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7313,7 +7309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7327,10 +7323,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45187</v>
+        <v>45153</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,8 +7338,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>16.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7386,7 +7387,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7396,14 +7397,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45250</v>
+        <v>45664</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7415,8 +7416,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7459,7 +7465,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7473,10 +7479,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44833</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7489,7 +7495,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>24.6</v>
+        <v>43.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7532,7 +7538,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7546,10 +7552,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44833</v>
+        <v>45455</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7561,8 +7567,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>23.2</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7605,7 +7616,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7619,10 +7630,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45859</v>
+        <v>45832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7635,7 +7646,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7678,7 +7689,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7692,10 +7703,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45315</v>
+        <v>45079</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7707,8 +7718,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.1</v>
+        <v>22.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7751,7 +7767,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7761,14 +7777,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45079</v>
+        <v>45636</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7782,11 +7798,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>22.7</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7829,7 +7845,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7839,14 +7855,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45903</v>
+        <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7858,8 +7874,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7902,7 +7923,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7916,10 +7937,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>44732</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7931,8 +7952,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>9.199999999999999</v>
+        <v>39</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7975,7 +8001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7989,10 +8015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45905</v>
+        <v>45079</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8004,8 +8030,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8048,7 +8079,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8062,10 +8093,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45832</v>
+        <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8077,8 +8108,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>23.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8121,7 +8157,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8131,14 +8167,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45664</v>
+        <v>46104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8152,11 +8188,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>31.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8199,7 +8235,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8209,14 +8245,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44732</v>
+        <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8234,7 +8270,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>39</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8277,7 +8313,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8291,10 +8327,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>45859</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8307,7 +8343,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8350,7 +8386,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46747-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8364,10 +8400,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45926</v>
+        <v>45903</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8380,7 +8416,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>19.7</v>
+        <v>10</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8423,7 +8459,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8437,10 +8473,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45455</v>
+        <v>45905</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8452,13 +8488,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8501,7 +8532,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8511,14 +8542,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45825</v>
+        <v>45649</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8532,11 +8563,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>23.7</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8579,7 +8610,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8589,14 +8620,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8608,13 +8639,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8657,7 +8683,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8671,10 +8697,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45730</v>
+        <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8687,7 +8713,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8730,7 +8756,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8744,10 +8770,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45079</v>
+        <v>46139</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8759,13 +8785,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8808,7 +8829,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8822,10 +8843,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44473</v>
+        <v>45187</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8838,7 +8859,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8881,7 +8902,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8895,10 +8916,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45845</v>
+        <v>46139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8911,7 +8932,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8954,7 +8975,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8968,10 +8989,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45034</v>
+        <v>46139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8983,13 +9004,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>20.3</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9032,7 +9048,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9042,14 +9058,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45636</v>
+        <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9061,13 +9077,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9110,7 +9121,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9124,10 +9135,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44701</v>
+        <v>45216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9140,7 +9151,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9183,7 +9194,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9197,10 +9208,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45993</v>
+        <v>44874</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9213,7 +9224,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9256,7 +9267,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 46747-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9270,10 +9281,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45999</v>
+        <v>45926</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9286,7 +9297,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>11.3</v>
+        <v>19.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9329,7 +9340,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9343,10 +9354,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45999</v>
+        <v>44473</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9359,7 +9370,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9402,7 +9413,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9416,10 +9427,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45079</v>
+        <v>44741</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9431,13 +9442,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>29</v>
+        <v>15.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9480,7 +9486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9490,14 +9496,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46104</v>
+        <v>45937</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9515,7 +9521,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>31.7</v>
+        <v>6.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9558,7 +9564,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9572,10 +9578,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45281</v>
+        <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9588,7 +9594,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>13.4</v>
+        <v>7.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9631,7 +9637,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9641,14 +9647,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44735</v>
+        <v>45825</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9662,11 +9668,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>25.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9709,7 +9715,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9723,10 +9729,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46139</v>
+        <v>46162</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9739,7 +9745,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9782,7 +9788,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9792,14 +9798,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45183</v>
+        <v>45315</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9811,13 +9817,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9860,7 +9861,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9874,10 +9875,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46139</v>
+        <v>45463</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9889,8 +9890,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>30.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9933,7 +9939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9947,10 +9953,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45625</v>
+        <v>45468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9963,7 +9969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>11.5</v>
+        <v>6.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10006,7 +10012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10020,10 +10026,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46139</v>
+        <v>45614</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10036,7 +10042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10079,7 +10085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10089,14 +10095,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45649</v>
+        <v>46181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10108,13 +10114,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>16.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10157,7 +10158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10167,14 +10168,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45469</v>
+        <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10186,8 +10187,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10230,7 +10236,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10244,10 +10250,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45469</v>
+        <v>45625</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10260,7 +10266,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10303,7 +10309,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10313,14 +10319,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44735</v>
+        <v>45625</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10332,13 +10338,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10381,7 +10382,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10395,10 +10396,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44741</v>
+        <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10410,8 +10411,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>15.6</v>
+        <v>14.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10454,7 +10460,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10468,10 +10474,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45825</v>
+        <v>45845</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10483,13 +10489,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>25.1</v>
+        <v>4.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10532,7 +10533,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10546,10 +10547,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46162</v>
+        <v>45625</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10562,7 +10563,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10605,7 +10606,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10619,10 +10620,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44874</v>
+        <v>45625</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10635,7 +10636,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10678,7 +10679,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10692,10 +10693,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46162</v>
+        <v>46198</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10707,8 +10708,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>7.7</v>
+        <v>18</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10751,7 +10757,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10765,10 +10771,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45463</v>
+        <v>46198</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10786,7 +10792,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>30.7</v>
+        <v>11.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10829,7 +10835,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10843,10 +10849,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45467</v>
+        <v>45034</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10858,8 +10864,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>17.2</v>
+        <v>20.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10902,7 +10913,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10916,10 +10927,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45281</v>
+        <v>45730</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10932,7 +10943,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>43.6</v>
+        <v>4.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10975,7 +10986,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10985,14 +10996,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45614</v>
+        <v>46252</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11004,8 +11015,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11048,7 +11064,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11058,14 +11074,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45468</v>
+        <v>44735</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11077,8 +11093,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11121,7 +11142,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11135,10 +11156,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46181</v>
+        <v>45993</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11151,7 +11172,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>16.9</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11194,7 +11215,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11208,10 +11229,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11229,7 +11250,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11272,7 +11293,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11282,14 +11303,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45730</v>
+        <v>45183</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11301,8 +11322,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11345,7 +11371,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11362,7 +11388,7 @@
         <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11380,7 +11406,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>18</v>
+        <v>13.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11423,7 +11449,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11433,14 +11459,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11458,7 +11484,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11501,7 +11527,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11515,10 +11541,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11536,7 +11562,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11579,7 +11605,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11593,10 +11619,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45530</v>
+        <v>46197</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11608,8 +11634,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11652,7 +11683,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11662,14 +11693,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46252</v>
+        <v>45999</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11681,13 +11712,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>11.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11730,7 +11756,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11740,14 +11766,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46189</v>
+        <v>45999</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11759,13 +11785,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11808,7 +11829,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11818,14 +11839,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45153</v>
+        <v>46266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11843,7 +11864,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>16.9</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11886,7 +11907,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11900,10 +11921,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11915,13 +11936,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>17.2</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11964,7 +11980,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11978,10 +11994,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11993,13 +12009,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12042,7 +12053,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12052,14 +12063,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46197</v>
+        <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12073,11 +12084,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>13.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12120,7 +12131,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12134,10 +12145,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46197</v>
+        <v>46028</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12149,13 +12160,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12198,7 +12204,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12212,10 +12218,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45281</v>
+        <v>45583</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12228,7 +12234,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12271,7 +12277,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12281,14 +12287,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45625</v>
+        <v>45250</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12301,7 +12307,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>11.2</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12344,7 +12350,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12354,14 +12360,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46266</v>
+        <v>45730</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12373,13 +12379,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12422,7 +12423,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12436,10 +12437,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45625</v>
+        <v>45079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12451,8 +12452,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12495,7 +12501,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12509,10 +12515,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46028</v>
+        <v>45621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12525,7 +12531,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>19.5</v>
+        <v>11.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12568,7 +12574,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12582,10 +12588,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46269</v>
+        <v>44701</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12597,13 +12603,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>13.9</v>
+        <v>20.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12646,7 +12647,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12660,10 +12661,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45625</v>
+        <v>44830</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12675,8 +12676,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12719,7 +12725,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12729,14 +12735,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>44479</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12749,7 +12755,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>19.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12792,7 +12798,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12806,10 +12812,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44830</v>
+        <v>44833</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12821,13 +12827,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>6.5</v>
+        <v>24.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12870,7 +12871,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12880,14 +12881,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44479</v>
+        <v>44833</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12900,7 +12901,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>19.8</v>
+        <v>23.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12960,7 +12961,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE137"/>
+  <dimension ref="A1:AE138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T5" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U5" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,6 @@
 Kristallskinn
 Kötticka
 Rosenticka
-Rutspindling
 Rynkskinn
 Skrovellav
 Talltita
@@ -1220,7 +1219,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1360,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1506,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1647,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1792,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1929,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2068,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2185,7 +2184,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30617-2025</t>
+          <t>A 38453-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2199,10 +2198,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45831</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2214,28 +2213,23 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>39.8</v>
+        <v>13.8</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
       </c>
       <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
-        <v>13</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5</v>
-      </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2247,18 +2241,156 @@
         <v>19</v>
       </c>
       <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>41</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Gräddporing
+Blanksvart spiklav
+Blågrå svartspik
+Brunpudrad nållav
+Dropptaggsvamp
+Dvärgbägarlav
+Knottrig blåslav
+Kolflarnlav
+Lavskrika
+Mörk kolflarnlav
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Luddlav
+Skinnlav
+Stuplav
+Vedticka
+Ögonpyrola
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 38453-2026 artfynd.xlsx", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 38453-2026 karta.png", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 38453-2026 georefererad karta.tif", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 38453-2026 FSC-klagomål.docx", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 38453-2026 FSC-klagomål mail.docx", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 38453-2026 tillsynsbegäran.docx", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 38453-2026 tillsynsbegäran mail.docx", "A 38453-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 38453-2026 prioriterade fågelarter.docx", "A 38453-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 30617-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45831</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>19</v>
+      </c>
+      <c r="R14" t="n">
         <v>6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>23</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>73</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>73</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -2285,115 +2417,115 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 30617-2025 artfynd.xlsx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 30617-2025 karta.png", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 30617-2025 georefererad karta.tif", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/knärot/A 30617-2025 karta knärot.png", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 30617-2025 FSC-klagomål.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 30617-2025 FSC-klagomål mail.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 30617-2025 tillsynsbegäran.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 30617-2025 tillsynsbegäran mail.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 30617-2025 prioriterade fågelarter.docx", "A 30617-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 64817-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>7.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>13</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>16</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>22</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>36</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>36</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -2419,111 +2551,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64817-2023 artfynd.xlsx", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64817-2023 karta.png", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64817-2023 georefererad karta.tif", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64817-2023 FSC-klagomål.docx", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64817-2023 FSC-klagomål mail.docx", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64817-2023 tillsynsbegäran.docx", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64817-2023 tillsynsbegäran mail.docx", "A 64817-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64817-2023 prioriterade fågelarter.docx", "A 64817-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 34430-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45845</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>39.6</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>9</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>14</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>15</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>20</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>66</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>66</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Blanksvart spiklav
@@ -2547,116 +2679,116 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 34430-2025 artfynd.xlsx", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 34430-2025 karta.png", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 34430-2025 georefererad karta.tif", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 34430-2025 FSC-klagomål.docx", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 34430-2025 FSC-klagomål mail.docx", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 34430-2025 tillsynsbegäran.docx", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 34430-2025 tillsynsbegäran mail.docx", "A 34430-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 34430-2025 prioriterade fågelarter.docx", "A 34430-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 47035-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44851</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>15.9</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>11</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>9</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>18</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>40</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>33</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Månlåsbräken
 Öring
@@ -2678,107 +2810,237 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 47035-2022 artfynd.xlsx", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 47035-2022 karta.png", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 47035-2022 georefererad karta.tif", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 47035-2022 FSC-klagomål.docx", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 47035-2022 FSC-klagomål mail.docx", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 47035-2022 tillsynsbegäran.docx", "A 47035-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 47035-2022 tillsynsbegäran mail.docx", "A 47035-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 64805-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>55</v>
+      </c>
+      <c r="U18" t="n">
+        <v>55</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Skrovellav
+Tretåig hackspett
+Ullticka
+Vedtrappmossa
+Blodticka
+Bårdlav
+Luddlav
+Stuplav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64805-2023 artfynd.xlsx", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64805-2023 karta.png", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64805-2023 georefererad karta.tif", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64805-2023 FSC-klagomål.docx", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64805-2023 FSC-klagomål mail.docx", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64805-2023 tillsynsbegäran.docx", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64805-2023 tillsynsbegäran mail.docx", "A 64805-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64805-2023 prioriterade fågelarter.docx", "A 64805-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 64837-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L19" t="n">
         <v>12</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>14</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R19" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S19" t="n">
         <v>17</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>57</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>57</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -2799,241 +3061,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64837-2023 artfynd.xlsx", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64837-2023 karta.png", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64837-2023 georefererad karta.tif", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64837-2023 FSC-klagomål.docx", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64837-2023 FSC-klagomål mail.docx", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64837-2023 tillsynsbegäran.docx", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64837-2023 tillsynsbegäran mail.docx", "A 64837-2023")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64837-2023 prioriterade fågelarter.docx", "A 64837-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 64805-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 24892-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>9</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="D20" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>12</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13</v>
+      </c>
+      <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="S18" t="n">
-        <v>17</v>
-      </c>
-      <c r="T18" t="n">
-        <v>55</v>
-      </c>
-      <c r="U18" t="n">
-        <v>55</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Skrovellav
-Tretåig hackspett
-Ullticka
-Vedtrappmossa
-Blodticka
-Bårdlav
-Luddlav
-Stuplav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64805-2023 artfynd.xlsx", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64805-2023 karta.png", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64805-2023 georefererad karta.tif", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64805-2023 FSC-klagomål.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64805-2023 FSC-klagomål mail.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64805-2023 tillsynsbegäran.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64805-2023 tillsynsbegäran mail.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64805-2023 prioriterade fågelarter.docx", "A 64805-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24892-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>13</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>16</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>20</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -3053,116 +3185,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 24892-2026 artfynd.xlsx", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 24892-2026 karta.png", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 24892-2026 georefererad karta.tif", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 24892-2026 FSC-klagomål.docx", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 24892-2026 FSC-klagomål mail.docx", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 24892-2026 tillsynsbegäran.docx", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 24892-2026 tillsynsbegäran mail.docx", "A 24892-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 24892-2026 prioriterade fågelarter.docx", "A 24892-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 2256-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>17.9</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>8</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>11</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>31</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hökuggla
 Månlåsbräken
@@ -3177,116 +3309,239 @@
 Fjällummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 2256-2025 artfynd.xlsx", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 2256-2025 karta.png", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 2256-2025 georefererad karta.tif", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 2256-2025 FSC-klagomål.docx", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 2256-2025 FSC-klagomål mail.docx", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 2256-2025 tillsynsbegäran.docx", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 2256-2025 tillsynsbegäran mail.docx", "A 2256-2025")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 2256-2025 prioriterade fågelarter.docx", "A 2256-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
+        <v>13</v>
+      </c>
+      <c r="U22" t="n">
+        <v>11</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 45031-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45190</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>10.3</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M23" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>8</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R23" t="n">
         <v>4</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>10</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>14</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3300,112 +3555,353 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>20</v>
+      </c>
+      <c r="U24" t="n">
+        <v>20</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>13</v>
+      </c>
+      <c r="U25" t="n">
+        <v>11</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 1479-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M26" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>8</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R26" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S26" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T26" t="n">
         <v>16</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U26" t="n">
         <v>14</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3419,471 +3915,107 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 31143-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="D27" s="1" t="n">
+        <v>45831</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>6</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M27" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>9</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R27" t="n">
         <v>3</v>
       </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>13</v>
-      </c>
-      <c r="U23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="S27" t="n">
         <v>9</v>
       </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13</v>
-      </c>
-      <c r="U24" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>10</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20</v>
-      </c>
-      <c r="U25" t="n">
-        <v>20</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 31143-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45831</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>9</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>25</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>25</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -3896,111 +4028,348 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 31143-2025 artfynd.xlsx", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 31143-2025 karta.png", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 31143-2025 georefererad karta.tif", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 31143-2025 FSC-klagomål.docx", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 31143-2025 FSC-klagomål mail.docx", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 31143-2025 tillsynsbegäran.docx", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 31143-2025 tillsynsbegäran mail.docx", "A 31143-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 31143-2025 prioriterade fågelarter.docx", "A 31143-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 4544-2024</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45327</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>6</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R30" t="n">
         <v>2</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T30" t="n">
         <v>17</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4012,116 +4381,228 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="D31" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>13</v>
+      </c>
+      <c r="U31" t="n">
+        <v>13</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>8</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S32" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T32" t="n">
         <v>9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U32" t="n">
         <v>7</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4133,465 +4614,116 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 49079-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="D33" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
         <v>6</v>
       </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>9</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="T33" t="n">
         <v>6</v>
       </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" t="n">
-        <v>13</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 49079-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Lunglav
@@ -4601,107 +4733,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 49079-2025 artfynd.xlsx", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 49079-2025 karta.png", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 49079-2025 georefererad karta.tif", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 49079-2025 FSC-klagomål.docx", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 49079-2025 FSC-klagomål mail.docx", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 49079-2025 tillsynsbegäran.docx", "A 49079-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 49079-2025 tillsynsbegäran mail.docx", "A 49079-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 59199-2021</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>44490</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>16.2</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>5</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>9</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Gammelgransskål
@@ -4710,112 +4842,112 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 25229-2023</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45079</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>18.2</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>5</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Gammelgransskål
@@ -4824,111 +4956,111 @@
 Tretåig hackspett</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 64803-2023</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>43</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>4</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>4</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Gullmurkling
 Lunglav
@@ -4936,107 +5068,107 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 12403-2025</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>45730</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="E37" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>10.1</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>4</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S37" t="n">
         <v>4</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>9</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>9</v>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -5044,811 +5176,701 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AE36">
+      <c r="AE37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15171-2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>44658</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>48</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="Y38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 26143-2024</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>45467</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="E39" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>8.1</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L39" t="n">
         <v>2</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>2</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>3</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T39" t="n">
         <v>3</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U39" t="n">
         <v>3</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Knottrig blåslav
 Vedticka</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15171-2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 10525-2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
-        <v>44658</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>48</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="D40" s="1" t="n">
+        <v>45366</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J40" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="K40" t="n">
         <v>3</v>
       </c>
-      <c r="T38" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>3</v>
       </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Tretåig hackspett
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A 10525-2024</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>45366</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="T40" t="n">
         <v>4</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Spindelblomster
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>A 36564-2026</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D41" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="E41" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I41" t="n">
         <v>21.5</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>2</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>5</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Blå taggsvamp
 Kolflarnlav
 Stuplav</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 41375-2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45559</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Brudsporre</t>
+        </is>
+      </c>
+      <c r="W42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="Y42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>A 45324-2022</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D43" s="1" t="n">
         <v>44841</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
+      <c r="E43" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
         <v>23.2</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J43" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S43" t="n">
         <v>2</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T43" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>Bergand
 Sångsvan</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE43">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 41375-2024</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>45559</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Brudsporre</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>A 12789-2022</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>44642</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12789-2022 artfynd.xlsx", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12789-2022 karta.png", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12789-2022 georefererad karta.tif", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12789-2022 FSC-klagomål.docx", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12789-2022 FSC-klagomål mail.docx", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12789-2022 tillsynsbegäran.docx", "A 12789-2022")</f>
-        <v/>
-      </c>
-      <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12789-2022 tillsynsbegäran mail.docx", "A 12789-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 12789-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5862,10 +5884,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46076</v>
+        <v>44642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5877,32 +5899,37 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>56.1</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
         <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5914,39 +5941,39 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12789-2022 artfynd.xlsx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12789-2022 karta.png", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12789-2022 georefererad karta.tif", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12789-2022 FSC-klagomål.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12789-2022 FSC-klagomål mail.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12789-2022 tillsynsbegäran.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12789-2022 tillsynsbegäran mail.docx", "A 12789-2022")</f>
         <v/>
       </c>
     </row>
@@ -5970,7 +5997,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6058,7 +6085,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6072,10 +6099,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6088,16 +6115,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>18.8</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6112,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6124,50 +6151,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6181,10 +6204,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45079</v>
+        <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6196,23 +6219,18 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>18.8</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
@@ -6226,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6242,42 +6260,46 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 66844-2021</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6291,10 +6313,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44520</v>
+        <v>45079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6306,14 +6328,19 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>44.8</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6337,20 +6364,52 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56274-2021</t>
+          <t>A 66844-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6364,10 +6423,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44479</v>
+        <v>44520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6380,7 +6439,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.6</v>
+        <v>44.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6423,7 +6482,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56275-2021</t>
+          <t>A 56274-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6440,7 +6499,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6453,7 +6512,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>16.2</v>
+        <v>6.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6496,7 +6555,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56277-2021</t>
+          <t>A 56275-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6506,14 +6565,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6526,7 +6585,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>19.4</v>
+        <v>16.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6569,7 +6628,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44751-2022</t>
+          <t>A 56277-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6579,14 +6638,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44840</v>
+        <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6598,13 +6657,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>26.1</v>
+        <v>19.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6647,7 +6701,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56278-2021</t>
+          <t>A 44751-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6661,10 +6715,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44479</v>
+        <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6676,8 +6730,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>26.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6720,7 +6779,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52573-2022</t>
+          <t>A 56278-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6734,10 +6793,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44874</v>
+        <v>44479</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6750,7 +6809,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6793,7 +6852,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19620-2022</t>
+          <t>A 52573-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6803,14 +6862,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44694</v>
+        <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6822,13 +6881,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6871,7 +6925,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72279-2021</t>
+          <t>A 19620-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6885,10 +6939,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44543</v>
+        <v>44694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,8 +6954,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6944,7 +7003,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58879-2021</t>
+          <t>A 72279-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6954,14 +7013,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44489</v>
+        <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6974,7 +7033,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7017,7 +7076,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 58879-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7031,10 +7090,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45625</v>
+        <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7047,7 +7106,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.2</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7090,7 +7149,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7104,10 +7163,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45618</v>
+        <v>45583</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7120,7 +7179,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>18.3</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7163,7 +7222,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7177,10 +7236,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45467</v>
+        <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7193,7 +7252,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7236,7 +7295,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7246,14 +7305,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45530</v>
+        <v>44475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7265,8 +7324,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7309,7 +7373,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7323,10 +7387,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45153</v>
+        <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7338,13 +7402,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7387,7 +7446,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7397,14 +7456,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45664</v>
+        <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7416,13 +7475,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7465,7 +7519,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7475,14 +7529,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>45250</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7549,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>43.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7538,7 +7592,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7552,10 +7606,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45455</v>
+        <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7567,13 +7621,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>9.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7616,7 +7665,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7626,14 +7675,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45832</v>
+        <v>45664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7645,8 +7694,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7689,7 +7743,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7703,10 +7757,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45079</v>
+        <v>45455</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7720,11 +7774,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>22.7</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7767,7 +7821,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7777,14 +7831,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45636</v>
+        <v>44473</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7796,13 +7850,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7845,7 +7894,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7855,14 +7904,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44475</v>
+        <v>46139</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7874,13 +7923,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7923,7 +7967,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7937,10 +7981,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44732</v>
+        <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7952,13 +7996,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>39</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -8001,7 +8040,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8015,10 +8054,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45079</v>
+        <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8030,13 +8069,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>20.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8079,7 +8113,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8093,10 +8127,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45825</v>
+        <v>45859</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8108,13 +8142,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>23.7</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8157,7 +8186,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8171,10 +8200,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46104</v>
+        <v>45903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8186,13 +8215,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>31.7</v>
+        <v>10</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8235,7 +8259,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8245,14 +8269,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44735</v>
+        <v>45905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8264,13 +8288,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8313,7 +8332,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8327,10 +8346,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45859</v>
+        <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8343,7 +8362,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8386,7 +8405,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8400,10 +8419,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45903</v>
+        <v>46139</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8416,7 +8435,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8459,7 +8478,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8473,10 +8492,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45905</v>
+        <v>45469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8489,7 +8508,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8532,7 +8551,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8542,14 +8561,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45649</v>
+        <v>45469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8561,13 +8580,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8610,7 +8624,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8624,10 +8638,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>45216</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8640,7 +8654,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8683,7 +8697,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 46747-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8697,10 +8711,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45469</v>
+        <v>45926</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8713,7 +8727,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.1</v>
+        <v>19.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8756,7 +8770,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8770,10 +8784,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46139</v>
+        <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8786,7 +8800,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>15.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8829,7 +8843,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8839,14 +8853,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45187</v>
+        <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8858,8 +8872,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8902,7 +8921,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8916,10 +8935,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46139</v>
+        <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8932,7 +8951,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>13.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8975,7 +8994,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8985,14 +9004,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46139</v>
+        <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9004,8 +9023,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9048,7 +9072,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9062,10 +9086,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45469</v>
+        <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9078,7 +9102,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9121,7 +9145,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9131,14 +9155,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45216</v>
+        <v>45183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9150,8 +9174,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9194,7 +9223,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9208,10 +9237,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44874</v>
+        <v>45625</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9224,7 +9253,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9267,7 +9296,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46747-2025</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9281,10 +9310,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45926</v>
+        <v>45034</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9296,8 +9325,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9340,7 +9374,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9350,14 +9384,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44473</v>
+        <v>45649</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9369,8 +9403,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9413,7 +9452,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9427,10 +9466,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44741</v>
+        <v>45825</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9442,8 +9481,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>15.6</v>
+        <v>25.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9486,7 +9530,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9496,14 +9540,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45937</v>
+        <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9515,13 +9559,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9581,7 +9620,7 @@
         <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9637,7 +9676,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9647,14 +9686,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45825</v>
+        <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9668,11 +9707,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>25.1</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9715,7 +9754,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9729,10 +9768,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46162</v>
+        <v>45993</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9745,7 +9784,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9788,7 +9827,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9802,10 +9841,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45315</v>
+        <v>45999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9818,7 +9857,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.1</v>
+        <v>11.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9861,7 +9900,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9875,10 +9914,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45463</v>
+        <v>45999</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9890,13 +9929,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>30.7</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9939,7 +9973,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9953,10 +9987,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45468</v>
+        <v>44874</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9969,7 +10003,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10012,7 +10046,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10026,10 +10060,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45614</v>
+        <v>45463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10041,8 +10075,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>30.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10085,7 +10124,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10099,10 +10138,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46181</v>
+        <v>45730</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10115,7 +10154,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>16.9</v>
+        <v>7.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10158,7 +10197,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10168,14 +10207,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46188</v>
+        <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10187,13 +10226,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10236,7 +10270,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10250,10 +10284,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45625</v>
+        <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10265,8 +10299,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10309,7 +10348,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10323,10 +10362,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45625</v>
+        <v>45468</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10339,7 +10378,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10382,7 +10421,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10396,10 +10435,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46197</v>
+        <v>45467</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10411,13 +10450,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10460,7 +10494,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10474,10 +10508,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45845</v>
+        <v>45281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10490,7 +10524,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.3</v>
+        <v>43.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10533,7 +10567,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10547,10 +10581,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45625</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10563,7 +10597,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.3</v>
+        <v>16.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10606,7 +10640,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10616,14 +10650,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45625</v>
+        <v>45636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10635,8 +10669,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10679,7 +10718,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10689,14 +10728,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10710,11 +10749,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>18</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10757,7 +10796,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10771,10 +10810,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46198</v>
+        <v>45079</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10788,11 +10827,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10835,7 +10874,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10849,10 +10888,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45034</v>
+        <v>45730</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10864,13 +10903,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>20.3</v>
+        <v>4.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10913,7 +10947,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10927,10 +10961,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45730</v>
+        <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10942,8 +10976,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10986,7 +11025,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10996,14 +11035,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46252</v>
+        <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11017,11 +11056,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11064,7 +11103,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11074,14 +11113,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44735</v>
+        <v>46197</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11095,11 +11134,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>14.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11142,7 +11181,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11156,10 +11195,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45993</v>
+        <v>46104</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11171,8 +11210,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>31.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11215,7 +11259,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11225,14 +11269,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46189</v>
+        <v>45530</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11244,13 +11288,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11293,7 +11332,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11303,14 +11342,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45183</v>
+        <v>45153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11324,11 +11363,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5</v>
+        <v>16.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11371,7 +11410,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11385,10 +11424,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11400,13 +11439,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11449,7 +11483,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11463,10 +11497,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46197</v>
+        <v>46252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11480,11 +11514,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11527,7 +11561,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11541,10 +11575,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46198</v>
+        <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11556,13 +11590,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11605,7 +11634,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11615,14 +11644,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46197</v>
+        <v>46189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11636,11 +11665,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>22.9</v>
+        <v>0.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11683,7 +11712,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11697,10 +11726,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45999</v>
+        <v>46198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11712,8 +11741,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>11.3</v>
+        <v>17.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11756,7 +11790,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11770,10 +11804,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45999</v>
+        <v>45625</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11786,7 +11820,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11829,7 +11863,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11839,14 +11873,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46266</v>
+        <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11860,11 +11894,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>13.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11907,7 +11941,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11917,14 +11951,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45281</v>
+        <v>46197</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11936,8 +11970,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11980,7 +12019,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11994,10 +12033,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45281</v>
+        <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12009,8 +12048,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>13.4</v>
+        <v>22.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12053,7 +12097,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12063,14 +12107,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12088,7 +12132,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>13.9</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12131,7 +12175,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12145,10 +12189,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46028</v>
+        <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12161,7 +12205,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12204,7 +12248,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12218,10 +12262,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45583</v>
+        <v>45625</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12234,7 +12278,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12277,7 +12321,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12287,14 +12331,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45250</v>
+        <v>44830</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12306,8 +12350,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12350,7 +12399,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12364,10 +12413,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45730</v>
+        <v>46028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12380,7 +12429,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12423,7 +12472,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12437,10 +12486,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45079</v>
+        <v>46269</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12454,11 +12503,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7</v>
+        <v>13.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12501,7 +12550,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12511,14 +12560,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45621</v>
+        <v>44479</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12531,7 +12580,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11.3</v>
+        <v>19.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12574,7 +12623,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12588,10 +12637,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44701</v>
+        <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12604,7 +12653,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>20.3</v>
+        <v>24.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12647,7 +12696,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12661,10 +12710,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44830</v>
+        <v>44833</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12676,13 +12725,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>6.5</v>
+        <v>23.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12725,7 +12769,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12735,14 +12779,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44479</v>
+        <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12754,8 +12798,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>19.8</v>
+        <v>22.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12798,7 +12847,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12812,10 +12861,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44833</v>
+        <v>45832</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12828,7 +12877,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>24.6</v>
+        <v>4.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12871,7 +12920,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12885,10 +12934,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44833</v>
+        <v>44732</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12900,8 +12949,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>23.2</v>
+        <v>39</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12941,83 +12995,161 @@
       </c>
       <c r="V136" s="2" t="inlineStr"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
+          <t>A 29662-2025</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>S 1086-2023</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D137" s="1" t="n">
+      <c r="D138" s="1" t="n">
         <v>45013</v>
       </c>
-      <c r="E137" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
+      <c r="E138" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I137" t="n">
+      <c r="I138" t="n">
         <v>24.2</v>
       </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="2" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -1111,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="n">
+        <v>169</v>
+      </c>
+      <c r="U5" t="n">
         <v>168</v>
-      </c>
-      <c r="U5" t="n">
-        <v>167</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1140,6 +1140,7 @@
 Kristallskinn
 Kötticka
 Rosenticka
+Rutspindling
 Rynkskinn
 Skrovellav
 Talltita
@@ -1219,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1360,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1506,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1647,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1792,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1929,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2068,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2201,7 +2202,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2334,7 +2335,7 @@
         <v>45831</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2474,7 +2475,7 @@
         <v>45281</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2604,7 +2605,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2732,7 +2733,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2859,7 +2860,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2989,7 +2990,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3114,7 +3115,7 @@
         <v>46174</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3238,7 +3239,7 @@
         <v>45671</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3362,7 +3363,7 @@
         <v>45190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3485,7 +3486,7 @@
         <v>45190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3604,7 +3605,7 @@
         <v>45576</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3722,7 +3723,7 @@
         <v>46033</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3845,7 +3846,7 @@
         <v>46033</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3964,7 +3965,7 @@
         <v>45831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4081,7 +4082,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4202,7 +4203,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4318,7 +4319,7 @@
         <v>45327</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4434,7 +4435,7 @@
         <v>45818</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4546,7 +4547,7 @@
         <v>46033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4667,7 +4668,7 @@
         <v>45937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4782,7 +4783,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4891,7 +4892,7 @@
         <v>45079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5009,7 +5010,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5117,7 +5118,7 @@
         <v>45730</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5229,7 +5230,7 @@
         <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5340,7 +5341,7 @@
         <v>45467</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5447,7 +5448,7 @@
         <v>45366</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5554,7 +5555,7 @@
         <v>46269</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5666,7 +5667,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5777,7 +5778,7 @@
         <v>44841</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5887,7 +5888,7 @@
         <v>44642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5997,7 +5998,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6102,7 +6103,7 @@
         <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6207,7 +6208,7 @@
         <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6316,7 +6317,7 @@
         <v>45079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6426,7 +6427,7 @@
         <v>44520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6499,7 +6500,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6572,7 +6573,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6645,7 +6646,7 @@
         <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6718,7 +6719,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6796,7 +6797,7 @@
         <v>44479</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6869,7 +6870,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6942,7 +6943,7 @@
         <v>44694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7020,7 +7021,7 @@
         <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7093,7 +7094,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7166,7 +7167,7 @@
         <v>45583</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7239,7 +7240,7 @@
         <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7312,7 +7313,7 @@
         <v>44475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7390,7 +7391,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7464,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7536,7 +7537,7 @@
         <v>45250</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7609,7 +7610,7 @@
         <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7682,7 +7683,7 @@
         <v>45664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7760,7 +7761,7 @@
         <v>45455</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7838,7 +7839,7 @@
         <v>44473</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7911,7 +7912,7 @@
         <v>46139</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7984,7 +7985,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8057,7 +8058,7 @@
         <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8130,7 +8131,7 @@
         <v>45859</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8203,7 +8204,7 @@
         <v>45903</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8276,7 +8277,7 @@
         <v>45905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8349,7 +8350,7 @@
         <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8422,7 +8423,7 @@
         <v>46139</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8495,7 +8496,7 @@
         <v>45469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8568,7 +8569,7 @@
         <v>45469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8641,7 +8642,7 @@
         <v>45216</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8714,7 +8715,7 @@
         <v>45926</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8787,7 +8788,7 @@
         <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8860,7 +8861,7 @@
         <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8938,7 +8939,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9011,7 +9012,7 @@
         <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9089,7 +9090,7 @@
         <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9162,7 +9163,7 @@
         <v>45183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9240,7 +9241,7 @@
         <v>45625</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9314,7 @@
         <v>45034</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9391,7 +9392,7 @@
         <v>45649</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9469,7 +9470,7 @@
         <v>45825</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9547,7 +9548,7 @@
         <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9620,7 +9621,7 @@
         <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9693,7 +9694,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9771,7 +9772,7 @@
         <v>45993</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9844,7 +9845,7 @@
         <v>45999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9917,7 +9918,7 @@
         <v>45999</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9990,7 +9991,7 @@
         <v>44874</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10063,7 +10064,7 @@
         <v>45463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10141,7 +10142,7 @@
         <v>45730</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10214,7 +10215,7 @@
         <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10287,7 +10288,7 @@
         <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10365,7 +10366,7 @@
         <v>45468</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10438,7 +10439,7 @@
         <v>45467</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10511,7 +10512,7 @@
         <v>45281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10584,7 +10585,7 @@
         <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10657,7 +10658,7 @@
         <v>45636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10735,7 +10736,7 @@
         <v>46188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10813,7 +10814,7 @@
         <v>45079</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10891,7 +10892,7 @@
         <v>45730</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10964,7 +10965,7 @@
         <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11042,7 +11043,7 @@
         <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11120,7 +11121,7 @@
         <v>46197</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11198,7 +11199,7 @@
         <v>46104</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11276,7 +11277,7 @@
         <v>45530</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11349,7 +11350,7 @@
         <v>45153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11427,7 +11428,7 @@
         <v>45281</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11500,7 +11501,7 @@
         <v>46252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11578,7 +11579,7 @@
         <v>45625</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11651,7 +11652,7 @@
         <v>46189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11729,7 +11730,7 @@
         <v>46198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11807,7 +11808,7 @@
         <v>45625</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11880,7 +11881,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11958,7 +11959,7 @@
         <v>46197</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12036,7 +12037,7 @@
         <v>46197</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12114,7 +12115,7 @@
         <v>46266</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12192,7 +12193,7 @@
         <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12265,7 +12266,7 @@
         <v>45625</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12338,7 +12339,7 @@
         <v>44830</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12416,7 +12417,7 @@
         <v>46028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12489,7 +12490,7 @@
         <v>46269</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12567,7 +12568,7 @@
         <v>44479</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12640,7 +12641,7 @@
         <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12713,7 +12714,7 @@
         <v>44833</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12786,7 +12787,7 @@
         <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12864,7 +12865,7 @@
         <v>45832</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12937,7 +12938,7 @@
         <v>44732</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13015,7 +13016,7 @@
         <v>45825</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13093,7 +13094,7 @@
         <v>45013</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38453-2026</t>
+          <t>A 30617-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2214,23 +2214,28 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>13.8</v>
+        <v>39.8</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
       </c>
       <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
-        <v>16</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2242,156 +2247,18 @@
         <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Gräddporing
-Blanksvart spiklav
-Blågrå svartspik
-Brunpudrad nållav
-Dropptaggsvamp
-Dvärgbägarlav
-Knottrig blåslav
-Kolflarnlav
-Lavskrika
-Mörk kolflarnlav
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedflamlav
-Vedskivlav
-Vedtrappmossa
-Luddlav
-Skinnlav
-Stuplav
-Vedticka
-Ögonpyrola
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 38453-2026 artfynd.xlsx", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 38453-2026 karta.png", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 38453-2026 georefererad karta.tif", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 38453-2026 FSC-klagomål.docx", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 38453-2026 FSC-klagomål mail.docx", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 38453-2026 tillsynsbegäran.docx", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 38453-2026 tillsynsbegäran mail.docx", "A 38453-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 38453-2026 prioriterade fågelarter.docx", "A 38453-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30617-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45831</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>19</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>73</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -2418,115 +2285,115 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 30617-2025 artfynd.xlsx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 30617-2025 karta.png", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 30617-2025 georefererad karta.tif", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/knärot/A 30617-2025 karta knärot.png", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 30617-2025 FSC-klagomål.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 30617-2025 FSC-klagomål mail.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 30617-2025 tillsynsbegäran.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 30617-2025 tillsynsbegäran mail.docx", "A 30617-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 30617-2025 prioriterade fågelarter.docx", "A 30617-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 64817-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>7.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L14" t="n">
         <v>13</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>16</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R14" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S14" t="n">
         <v>22</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T14" t="n">
         <v>36</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U14" t="n">
         <v>36</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -2552,36 +2419,166 @@
 Spillkråka</t>
         </is>
       </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64817-2023 artfynd.xlsx", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64817-2023 karta.png", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64817-2023 georefererad karta.tif", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64817-2023 FSC-klagomål.docx", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64817-2023 FSC-klagomål mail.docx", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64817-2023 tillsynsbegäran.docx", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64817-2023 tillsynsbegäran mail.docx", "A 64817-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64817-2023 prioriterade fågelarter.docx", "A 64817-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38453-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>38</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Gräddporing
+Blanksvart spiklav
+Blågrå svartspik
+Brunpudrad nållav
+Dropptaggsvamp
+Dvärgbägarlav
+Knottrig blåslav
+Kolflarnlav
+Lavskrika
+Mörk kolflarnlav
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Luddlav
+Vedticka
+Ögonpyrola
+Tjäder</t>
+        </is>
+      </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64817-2023 artfynd.xlsx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 38453-2026 artfynd.xlsx", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64817-2023 karta.png", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 38453-2026 karta.png", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64817-2023 georefererad karta.tif", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 38453-2026 georefererad karta.tif", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64817-2023 FSC-klagomål.docx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 38453-2026 FSC-klagomål.docx", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64817-2023 FSC-klagomål mail.docx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 38453-2026 FSC-klagomål mail.docx", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64817-2023 tillsynsbegäran.docx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 38453-2026 tillsynsbegäran.docx", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64817-2023 tillsynsbegäran mail.docx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 38453-2026 tillsynsbegäran mail.docx", "A 38453-2026")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 64817-2023 prioriterade fågelarter.docx", "A 64817-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 38453-2026 prioriterade fågelarter.docx", "A 38453-2026")</f>
         <v/>
       </c>
     </row>
@@ -2605,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2733,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2860,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2990,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3115,7 +3112,7 @@
         <v>46174</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3239,7 +3236,7 @@
         <v>45671</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3363,7 +3360,7 @@
         <v>45190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3486,7 +3483,7 @@
         <v>45190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3605,7 +3602,7 @@
         <v>45576</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3723,7 +3720,7 @@
         <v>46033</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3846,7 +3843,7 @@
         <v>46033</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3965,7 +3962,7 @@
         <v>45831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4082,7 +4079,7 @@
         <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4203,7 +4200,7 @@
         <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4302,7 +4299,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 28351-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4316,10 +4313,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45327</v>
+        <v>45818</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4332,16 +4329,16 @@
         </is>
       </c>
       <c r="I30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
@@ -4356,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
         <v>2</v>
@@ -4365,12 +4362,124 @@
         <v>8</v>
       </c>
       <c r="T30" t="n">
+        <v>13</v>
+      </c>
+      <c r="U30" t="n">
+        <v>13</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
         <v>17</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4382,148 +4491,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" t="n">
-        <v>13</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
     </row>
@@ -4547,7 +4544,7 @@
         <v>46033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4668,7 +4665,7 @@
         <v>45937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4783,7 +4780,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4892,7 +4889,7 @@
         <v>45079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5010,7 +5007,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5118,7 +5115,7 @@
         <v>45730</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5230,7 +5227,7 @@
         <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5341,7 +5338,7 @@
         <v>45467</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5431,7 +5428,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10525-2024</t>
+          <t>A 36564-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5445,10 +5442,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45366</v>
+        <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5460,18 +5457,23 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>15.5</v>
+        <v>21.5</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -5485,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5494,156 +5496,151 @@
         <v>3</v>
       </c>
       <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp
+Kolflarnlav
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="Y40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AD40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A 10525-2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>45366</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
         <v>4</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Spindelblomster
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A 36564-2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp
-Kolflarnlav
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
     </row>
@@ -5667,7 +5664,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5778,7 +5775,7 @@
         <v>44841</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5888,7 +5885,7 @@
         <v>44642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5998,7 +5995,7 @@
         <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6103,7 +6100,7 @@
         <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6208,7 +6205,7 @@
         <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6317,7 +6314,7 @@
         <v>45079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6427,7 +6424,7 @@
         <v>44520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6500,7 +6497,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6573,7 +6570,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6643,7 @@
         <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6719,7 +6716,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6797,7 +6794,7 @@
         <v>44479</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6870,7 +6867,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6943,7 +6940,7 @@
         <v>44694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7021,7 +7018,7 @@
         <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7094,7 +7091,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7167,7 +7164,7 @@
         <v>45583</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7223,7 +7220,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7237,10 +7234,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7250,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>18.3</v>
+        <v>11.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7296,7 +7293,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7306,14 +7303,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44475</v>
+        <v>45618</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7325,13 +7322,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>18.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7374,7 +7366,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7384,14 +7376,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45621</v>
+        <v>44475</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7403,8 +7395,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>11.3</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7464,7 +7461,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7537,7 +7534,7 @@
         <v>45250</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7610,7 +7607,7 @@
         <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7683,7 +7680,7 @@
         <v>45664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7761,7 +7758,7 @@
         <v>45455</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7839,7 +7836,7 @@
         <v>44473</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7912,7 +7909,7 @@
         <v>46139</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7985,7 +7982,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8041,7 +8038,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8055,10 +8052,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44701</v>
+        <v>45859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8071,7 +8068,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>20.3</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8114,7 +8111,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8128,10 +8125,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45859</v>
+        <v>45903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8144,7 +8141,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8187,7 +8184,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8201,10 +8198,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45903</v>
+        <v>45905</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8217,7 +8214,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8260,7 +8257,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8277,7 +8274,7 @@
         <v>45905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8290,7 +8287,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8333,7 +8330,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8347,10 +8344,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45905</v>
+        <v>46139</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8363,7 +8360,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8406,7 +8403,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8420,10 +8417,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46139</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8436,7 +8433,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8479,7 +8476,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8493,10 +8490,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45469</v>
+        <v>44701</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8509,7 +8506,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.1</v>
+        <v>20.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8552,7 +8549,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8569,7 +8566,7 @@
         <v>45469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8582,7 +8579,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8625,7 +8622,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8639,10 +8636,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45216</v>
+        <v>45469</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8655,7 +8652,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8698,7 +8695,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46747-2025</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8712,10 +8709,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45926</v>
+        <v>44741</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8728,7 +8725,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>19.7</v>
+        <v>15.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8771,7 +8768,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8781,14 +8778,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44741</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8800,8 +8797,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>15.6</v>
+        <v>6.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8844,7 +8846,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8854,14 +8856,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45937</v>
+        <v>45825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,11 +8877,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.5</v>
+        <v>25.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8922,7 +8924,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8936,10 +8938,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45281</v>
+        <v>46162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8952,7 +8954,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>13.4</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8995,7 +8997,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9005,14 +9007,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44735</v>
+        <v>46162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9024,13 +9026,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9090,7 +9087,7 @@
         <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9146,7 +9143,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9156,14 +9153,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45183</v>
+        <v>45281</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9175,13 +9172,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>13.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9224,7 +9216,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9234,14 +9226,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45625</v>
+        <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9253,8 +9245,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>11.5</v>
+        <v>0.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9314,7 +9311,7 @@
         <v>45034</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9375,7 +9372,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9385,14 +9382,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45649</v>
+        <v>45993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9404,13 +9401,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9453,7 +9445,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9467,10 +9459,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45825</v>
+        <v>45999</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9482,13 +9474,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>25.1</v>
+        <v>11.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9531,7 +9518,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9545,10 +9532,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46162</v>
+        <v>45999</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9561,7 +9548,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9604,7 +9591,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9618,10 +9605,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46162</v>
+        <v>45614</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9634,7 +9621,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9677,7 +9664,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9687,14 +9674,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44735</v>
+        <v>45468</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9706,13 +9693,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9755,7 +9737,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9765,14 +9747,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45993</v>
+        <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9784,8 +9766,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9828,7 +9815,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9842,10 +9829,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45999</v>
+        <v>46181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9858,7 +9845,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>11.3</v>
+        <v>16.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9901,7 +9888,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9915,10 +9902,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45999</v>
+        <v>45625</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9931,7 +9918,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9974,7 +9961,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9984,14 +9971,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44874</v>
+        <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10003,8 +9990,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10047,7 +10039,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10057,14 +10049,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45463</v>
+        <v>45649</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10078,11 +10070,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>30.7</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10142,7 +10134,7 @@
         <v>45730</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10198,7 +10190,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10208,14 +10200,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45614</v>
+        <v>44735</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10227,8 +10219,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10288,7 +10285,7 @@
         <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10349,7 +10346,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10363,10 +10360,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45468</v>
+        <v>46198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10378,8 +10375,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10422,7 +10424,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10436,10 +10438,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45467</v>
+        <v>46198</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10451,8 +10453,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>17.2</v>
+        <v>11.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10495,7 +10502,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10509,10 +10516,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45281</v>
+        <v>46197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10524,8 +10531,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>43.6</v>
+        <v>14.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10568,7 +10580,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10578,14 +10590,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10597,8 +10609,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>16.9</v>
+        <v>3.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10641,7 +10658,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10651,14 +10668,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45636</v>
+        <v>45079</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10672,11 +10689,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>29</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10719,7 +10736,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10729,14 +10746,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46188</v>
+        <v>44874</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10748,13 +10765,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10797,7 +10809,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10811,10 +10823,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45079</v>
+        <v>45463</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10828,11 +10840,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>29</v>
+        <v>30.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10875,7 +10887,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10889,10 +10901,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45730</v>
+        <v>46104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10904,8 +10916,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>4.1</v>
+        <v>31.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10948,7 +10965,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10962,10 +10979,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46198</v>
+        <v>45467</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10977,13 +10994,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11026,7 +11038,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11040,10 +11052,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11055,13 +11067,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>11.5</v>
+        <v>43.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11104,7 +11111,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11114,14 +11121,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46197</v>
+        <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11135,11 +11142,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>14.2</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11182,7 +11189,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11192,14 +11199,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46104</v>
+        <v>46189</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11217,7 +11224,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>31.7</v>
+        <v>0.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11260,7 +11267,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11274,10 +11281,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45530</v>
+        <v>45730</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11290,7 +11297,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11333,7 +11340,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11347,10 +11354,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45153</v>
+        <v>46198</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11364,11 +11371,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11411,7 +11418,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11425,10 +11432,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45281</v>
+        <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11440,8 +11447,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>13.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11484,7 +11496,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11498,10 +11510,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46252</v>
+        <v>46197</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11515,11 +11527,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11562,7 +11574,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11576,10 +11588,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45625</v>
+        <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11591,8 +11603,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>11.2</v>
+        <v>22.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11635,7 +11652,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11649,10 +11666,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46189</v>
+        <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11670,7 +11687,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11713,7 +11730,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11727,10 +11744,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46198</v>
+        <v>45530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11742,13 +11759,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>17.2</v>
+        <v>20.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11791,7 +11803,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11805,10 +11817,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45625</v>
+        <v>46028</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11821,7 +11833,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>19.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11864,7 +11876,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11878,10 +11890,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46198</v>
+        <v>45153</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11895,11 +11907,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.3</v>
+        <v>16.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11942,7 +11954,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11952,14 +11964,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46197</v>
+        <v>46269</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11973,11 +11985,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.8</v>
+        <v>13.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12020,7 +12032,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12034,10 +12046,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46197</v>
+        <v>45281</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12049,13 +12061,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>22.9</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12098,7 +12105,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12108,14 +12115,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46266</v>
+        <v>45625</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12127,13 +12134,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12176,7 +12178,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12193,7 +12195,7 @@
         <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12206,7 +12208,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12249,7 +12251,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 38823-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12259,14 +12261,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45625</v>
+        <v>46286</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12278,8 +12280,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12322,7 +12329,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12336,10 +12343,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44830</v>
+        <v>45625</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12351,13 +12358,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12400,7 +12402,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12414,10 +12416,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46028</v>
+        <v>45625</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12430,7 +12432,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12473,7 +12475,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12487,10 +12489,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46269</v>
+        <v>44830</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12504,11 +12506,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>13.9</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12568,7 +12570,7 @@
         <v>44479</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12641,7 +12643,7 @@
         <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12714,7 +12716,7 @@
         <v>44833</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12787,7 +12789,7 @@
         <v>45079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12865,7 +12867,7 @@
         <v>45832</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12938,7 +12940,7 @@
         <v>44732</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13016,7 +13018,7 @@
         <v>45825</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13094,7 +13096,7 @@
         <v>45013</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE138"/>
+  <dimension ref="A1:AE139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46174</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45671</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45030-2023</t>
+          <t>A 45031-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3360,7 +3360,7 @@
         <v>45190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3378,19 +3378,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>10.3</v>
       </c>
       <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3402,21 +3402,140 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>14</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3430,116 +3549,234 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45031-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="D24" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>20</v>
+      </c>
+      <c r="U24" t="n">
+        <v>20</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>4</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>14</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3553,230 +3790,112 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="D26" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
         <v>10</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>20</v>
-      </c>
-      <c r="U24" t="n">
-        <v>20</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>13</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>11</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3790,155 +3909,36 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>8</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
-        <v>16</v>
-      </c>
-      <c r="U26" t="n">
-        <v>14</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Sprickporing
-Vitskaftad svartspik
-Gammelgransskål
-Rosenticka
-Ullticka
-Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
         <v>45831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45032-2023</t>
+          <t>A 4544-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45190</v>
+        <v>45327</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4091,22 +4091,17 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
@@ -4121,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
         <v>2</v>
@@ -4130,12 +4125,133 @@
         <v>8</v>
       </c>
       <c r="T28" t="n">
+        <v>17</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tajgaskinn
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Ullticka
+Blodticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
         <v>9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>7</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4147,111 +4263,111 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48673-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>32.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -4263,111 +4379,111 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 28351-2025</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45818</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>5.4</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>13</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>13</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4379,148 +4495,32 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 4544-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>17</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tajgaskinn
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Ullticka
-Blodticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
         <v>46033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45730</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15171-2022</t>
+          <t>A 10525-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44658</v>
+        <v>45366</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>48</v>
+        <v>15.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5273,374 +5273,374 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="Y38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>3</v>
       </c>
-      <c r="U38" t="n">
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 15171-2022</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>44658</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>48</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Tretåig hackspett
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AE38">
+      <c r="AE40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A 26143-2024</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A 36564-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
-        <v>45467</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
+      <c r="D41" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L41" t="n">
         <v>2</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 36564-2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>5</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Blå taggsvamp
 Kolflarnlav
 Stuplav</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A 10525-2024</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>45366</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>4</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44841</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45777</v>
+        <v>45034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.6</v>
+        <v>18.8</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -6048,42 +6048,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6097,10 +6101,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6112,8 +6116,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6149,46 +6158,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6202,10 +6211,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45034</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6218,10 +6227,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>18.8</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6258,46 +6267,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6311,10 +6316,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45079</v>
+        <v>46076</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6326,13 +6331,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6368,39 +6368,39 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
         <v>44520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44479</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45583</v>
+        <v>45649</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7176,8 +7176,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7220,7 +7225,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7230,14 +7235,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45621</v>
+        <v>44479</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7250,7 +7255,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11.3</v>
+        <v>19.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7293,7 +7298,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7307,10 +7312,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7328,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>18.3</v>
+        <v>11.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7366,7 +7371,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7376,14 +7381,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44475</v>
+        <v>45618</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7395,13 +7400,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>18.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7527,14 +7527,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45250</v>
+        <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45315</v>
+        <v>44473</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.1</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45664</v>
+        <v>45467</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7692,13 +7692,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>17.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7741,7 +7736,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7755,10 +7750,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45455</v>
+        <v>45859</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7770,13 +7765,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7819,7 +7809,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7833,10 +7823,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44473</v>
+        <v>45903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7849,7 +7839,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7892,7 +7882,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7906,10 +7896,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46139</v>
+        <v>45315</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7922,7 +7912,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>9.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7965,7 +7955,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7979,10 +7969,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46139</v>
+        <v>45905</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7995,7 +7985,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -8038,7 +8028,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8052,10 +8042,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45859</v>
+        <v>45905</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8068,7 +8058,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8111,7 +8101,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8125,10 +8115,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45903</v>
+        <v>45463</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8140,8 +8130,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>30.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8184,7 +8179,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8198,10 +8193,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45905</v>
+        <v>45530</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8214,7 +8209,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9.199999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8257,7 +8252,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8267,14 +8262,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45905</v>
+        <v>45664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8286,8 +8281,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8330,7 +8330,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46139</v>
+        <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8403,7 +8403,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>43.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44701</v>
+        <v>45153</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,8 +8505,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>20.3</v>
+        <v>16.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8549,7 +8554,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8563,10 +8568,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45469</v>
+        <v>44833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8579,7 +8584,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.1</v>
+        <v>24.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8622,7 +8627,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8636,10 +8641,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45469</v>
+        <v>44833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8652,7 +8657,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.199999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8695,7 +8700,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8705,14 +8710,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44741</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8724,8 +8729,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>15.6</v>
+        <v>6.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8768,7 +8778,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8778,14 +8788,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>45455</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8799,11 +8809,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8846,7 +8856,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8860,10 +8870,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45825</v>
+        <v>45625</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,13 +8885,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>25.1</v>
+        <v>11.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8924,7 +8929,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8938,10 +8943,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46162</v>
+        <v>45625</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8954,7 +8959,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8997,7 +9002,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9007,14 +9012,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46162</v>
+        <v>44475</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9026,8 +9031,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9070,7 +9080,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9084,10 +9094,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45845</v>
+        <v>45625</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9143,7 +9153,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9157,10 +9167,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45281</v>
+        <v>45625</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9173,7 +9183,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>13.4</v>
+        <v>7.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9216,7 +9226,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9226,14 +9236,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44735</v>
+        <v>45845</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9245,13 +9255,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9294,7 +9299,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9308,10 +9313,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45034</v>
+        <v>45730</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9323,13 +9328,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>20.3</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45993</v>
+        <v>45034</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9401,8 +9401,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>20.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9445,7 +9450,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9455,14 +9460,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45999</v>
+        <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9474,8 +9479,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9518,7 +9528,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9528,14 +9538,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45999</v>
+        <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9547,8 +9557,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9591,7 +9606,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9605,10 +9620,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45614</v>
+        <v>45832</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9621,7 +9636,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9664,7 +9679,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9678,10 +9693,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45468</v>
+        <v>45993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9694,7 +9709,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9737,7 +9752,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9747,14 +9762,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45183</v>
+        <v>45079</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9768,11 +9783,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>22.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9815,7 +9830,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9829,10 +9844,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46181</v>
+        <v>45999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9845,7 +9860,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9888,7 +9903,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9902,10 +9917,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45625</v>
+        <v>45999</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9918,7 +9933,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9961,7 +9976,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9975,10 +9990,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46188</v>
+        <v>45183</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9992,11 +10007,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10039,7 +10054,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10049,14 +10064,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45649</v>
+        <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10074,7 +10089,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>39</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10117,7 +10132,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10131,10 +10146,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10147,7 +10162,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10190,7 +10205,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10200,14 +10215,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44735</v>
+        <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10219,13 +10234,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10285,7 +10295,7 @@
         <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10346,7 +10356,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 38823-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10356,14 +10366,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46198</v>
+        <v>46286</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10377,11 +10387,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10424,7 +10434,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10438,10 +10448,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10453,13 +10463,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>11.5</v>
+        <v>13.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10502,7 +10507,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10512,14 +10517,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46197</v>
+        <v>45636</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10533,11 +10538,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10580,7 +10585,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 39456-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10590,14 +10595,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45636</v>
+        <v>46288</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10609,13 +10614,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.5</v>
+        <v>16.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10658,7 +10658,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45079</v>
+        <v>45583</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10687,13 +10687,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>29</v>
+        <v>3.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10736,7 +10731,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10746,14 +10741,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44874</v>
+        <v>45250</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10766,7 +10761,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10809,7 +10804,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10823,10 +10818,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45463</v>
+        <v>45079</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10840,11 +10835,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>30.7</v>
+        <v>29</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10887,7 +10882,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10901,10 +10896,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46104</v>
+        <v>45825</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10918,11 +10913,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>31.7</v>
+        <v>23.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10965,7 +10960,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10979,10 +10974,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45467</v>
+        <v>46104</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10994,8 +10989,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>17.2</v>
+        <v>31.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11038,7 +11038,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45281</v>
+        <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>43.6</v>
+        <v>11.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11111,7 +11111,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11121,14 +11121,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46252</v>
+        <v>44701</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11140,13 +11140,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>20.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11189,7 +11184,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11199,14 +11194,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46189</v>
+        <v>45469</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11218,13 +11213,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.1</v>
+        <v>7.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11267,7 +11257,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11281,10 +11271,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45730</v>
+        <v>46139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11297,7 +11287,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11340,7 +11330,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11354,10 +11344,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46198</v>
+        <v>46139</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11369,13 +11359,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>17.2</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11418,7 +11403,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11432,10 +11417,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46198</v>
+        <v>46139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11447,13 +11432,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>13.3</v>
+        <v>3.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11496,7 +11476,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11506,14 +11486,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46197</v>
+        <v>45469</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11525,13 +11505,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11574,7 +11549,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11588,10 +11563,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46197</v>
+        <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11605,11 +11580,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>22.9</v>
+        <v>6.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11652,7 +11627,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11662,14 +11637,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46266</v>
+        <v>44741</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11681,13 +11656,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11730,7 +11700,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11744,10 +11714,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45530</v>
+        <v>46162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11760,7 +11730,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>20.1</v>
+        <v>7.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11803,7 +11773,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11817,10 +11787,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46028</v>
+        <v>45825</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11832,8 +11802,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>19.5</v>
+        <v>25.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11876,7 +11851,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11890,10 +11865,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45153</v>
+        <v>46162</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11905,13 +11880,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>16.9</v>
+        <v>6.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11954,7 +11924,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11968,10 +11938,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46269</v>
+        <v>45468</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11983,13 +11953,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>13.9</v>
+        <v>6.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12032,7 +11997,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12046,10 +12011,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45281</v>
+        <v>45614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12062,7 +12027,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12105,7 +12070,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12119,10 +12084,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45625</v>
+        <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12135,7 +12100,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>11.2</v>
+        <v>16.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12178,7 +12143,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12188,14 +12153,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45625</v>
+        <v>46188</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12207,8 +12172,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12251,7 +12221,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 38823-2026</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12261,14 +12231,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46286</v>
+        <v>46197</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12282,11 +12252,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12329,7 +12299,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12343,10 +12313,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45625</v>
+        <v>46198</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12358,8 +12328,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>7.5</v>
+        <v>18</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12402,7 +12377,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12416,10 +12391,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45625</v>
+        <v>46198</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12431,8 +12406,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12475,7 +12455,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12485,14 +12465,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44830</v>
+        <v>46252</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12506,11 +12486,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12553,7 +12533,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12567,10 +12547,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44479</v>
+        <v>46189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12582,8 +12562,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>19.8</v>
+        <v>0.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12626,7 +12611,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12640,10 +12625,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44833</v>
+        <v>46198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12655,8 +12640,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>24.6</v>
+        <v>13.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12699,7 +12689,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12709,14 +12699,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44833</v>
+        <v>46197</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12728,8 +12718,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>23.2</v>
+        <v>4.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12772,7 +12767,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45079</v>
+        <v>46198</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12803,11 +12798,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>22.7</v>
+        <v>17.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12850,7 +12845,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12864,10 +12859,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45832</v>
+        <v>46197</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12879,8 +12874,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>4.3</v>
+        <v>22.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12933,14 +12933,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44732</v>
+        <v>46266</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12954,11 +12954,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>39</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13001,7 +13001,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45825</v>
+        <v>46269</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13032,11 +13032,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>23.7</v>
+        <v>13.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13076,83 +13076,156 @@
       </c>
       <c r="V137" s="2" t="inlineStr"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
+          <t>A 390-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>S 1086-2023</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D138" s="1" t="n">
+      <c r="D139" s="1" t="n">
         <v>45013</v>
       </c>
-      <c r="E138" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="E139" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I138" t="n">
+      <c r="I139" t="n">
         <v>24.2</v>
       </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="2" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46174</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45671</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45031-2023</t>
+          <t>A 45030-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3360,7 +3360,7 @@
         <v>45190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3378,19 +3378,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.3</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3402,21 +3402,144 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="n">
+        <v>13</v>
+      </c>
+      <c r="U22" t="n">
+        <v>11</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>14</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3430,112 +3553,230 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="D24" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>20</v>
+      </c>
+      <c r="U24" t="n">
+        <v>20</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>3.8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>6</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>9</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>13</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>11</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3549,234 +3790,116 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="D26" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
         <v>10</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>20</v>
-      </c>
-      <c r="U24" t="n">
-        <v>20</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>16</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>14</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3790,155 +3913,32 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
-        <v>13</v>
-      </c>
-      <c r="U26" t="n">
-        <v>11</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
         <v/>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
         <v>45831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 45032-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45327</v>
+        <v>45190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4091,17 +4091,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
@@ -4116,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R28" t="n">
         <v>2</v>
@@ -4125,12 +4130,356 @@
         <v>8</v>
       </c>
       <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>13</v>
+      </c>
+      <c r="U30" t="n">
+        <v>13</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
         <v>17</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4142,116 +4491,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="D32" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S32" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T32" t="n">
         <v>9</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U32" t="n">
         <v>7</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4263,355 +4612,6 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" t="n">
-        <v>13</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>9</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
       <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
@@ -4665,7 +4665,7 @@
         <v>45937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45079</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45730</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10525-2024</t>
+          <t>A 15171-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45366</v>
+        <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5240,17 +5240,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5273,262 +5273,262 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="Y38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A 10525-2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>45366</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
         <v>4</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Spindelblomster
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A 26143-2024</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>45467</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 15171-2022</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>44658</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>48</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Tretåig hackspett
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
         <v/>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
         <v>46269</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44841</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45034</v>
+        <v>45777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>18.8</v>
+        <v>10.6</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -6048,46 +6048,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6101,10 +6097,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45079</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6116,13 +6112,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6158,46 +6149,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6211,10 +6202,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>45034</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6227,10 +6218,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>18.8</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6267,42 +6258,46 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6316,10 +6311,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46076</v>
+        <v>45079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6331,8 +6326,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6368,39 +6368,39 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
         <v>44520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44479</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44543</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45649</v>
+        <v>45583</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7176,13 +7176,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7225,7 +7220,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7235,14 +7230,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44479</v>
+        <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7255,7 +7250,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7298,7 +7293,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7308,14 +7303,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45625</v>
+        <v>44475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7327,8 +7322,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>11.2</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7371,7 +7371,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>18.3</v>
+        <v>11.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7461,7 +7461,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7527,14 +7527,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44874</v>
+        <v>45250</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44473</v>
+        <v>45315</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>9.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45467</v>
+        <v>45664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7692,8 +7692,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>17.2</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7736,7 +7741,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7750,10 +7755,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45859</v>
+        <v>45455</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,8 +7770,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7809,7 +7819,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7823,10 +7833,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45903</v>
+        <v>44473</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7839,7 +7849,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7882,7 +7892,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7896,10 +7906,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45315</v>
+        <v>45859</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7912,7 +7922,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7955,7 +7965,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7969,10 +7979,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7985,7 +7995,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -8028,7 +8038,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8042,10 +8052,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8058,7 +8068,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8101,7 +8111,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8115,10 +8125,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45463</v>
+        <v>45905</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8130,13 +8140,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>30.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8179,7 +8184,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 42526-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8193,10 +8198,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45530</v>
+        <v>45905</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8209,7 +8214,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>20.1</v>
+        <v>12.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8252,7 +8257,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8262,14 +8267,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45664</v>
+        <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8281,13 +8286,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
         <v>45216</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45281</v>
+        <v>44701</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>43.6</v>
+        <v>20.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8486,14 +8486,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45153</v>
+        <v>45937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>16.9</v>
+        <v>6.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44833</v>
+        <v>46139</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>24.6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44833</v>
+        <v>45469</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>23.2</v>
+        <v>7.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8710,14 +8710,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8729,13 +8729,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8778,7 +8773,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8792,10 +8787,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45455</v>
+        <v>45281</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8807,13 +8802,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.9</v>
+        <v>13.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8856,7 +8846,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8870,10 +8860,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45625</v>
+        <v>45845</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8886,7 +8876,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8929,7 +8919,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8939,14 +8929,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45625</v>
+        <v>44735</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8958,8 +8948,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -9002,7 +8997,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9012,14 +9007,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44475</v>
+        <v>45034</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9033,11 +9028,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.1</v>
+        <v>20.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9080,7 +9075,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45625</v>
+        <v>44741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9110,7 +9105,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>15.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9153,7 +9148,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9167,10 +9162,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45625</v>
+        <v>45993</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9183,7 +9178,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9226,7 +9221,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9240,10 +9235,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45845</v>
+        <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9256,7 +9251,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>11.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9299,7 +9294,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9313,10 +9308,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45730</v>
+        <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9329,7 +9324,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9382,14 +9377,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45034</v>
+        <v>45183</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9403,11 +9398,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>20.3</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9450,7 +9445,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9460,14 +9455,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44735</v>
+        <v>45625</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9479,13 +9474,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9528,7 +9518,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9538,14 +9528,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44735</v>
+        <v>45825</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9559,11 +9549,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>25.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9606,7 +9596,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9620,10 +9610,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45832</v>
+        <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9636,7 +9626,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9679,7 +9669,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9693,10 +9683,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45993</v>
+        <v>46162</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9709,7 +9699,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9752,7 +9742,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9762,14 +9752,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45079</v>
+        <v>45649</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9787,7 +9777,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>22.7</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9830,7 +9820,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9840,14 +9830,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45999</v>
+        <v>44735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9859,8 +9849,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9903,7 +9898,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9917,10 +9912,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45999</v>
+        <v>45730</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9933,7 +9928,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9976,7 +9971,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9986,14 +9981,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45183</v>
+        <v>45079</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10007,11 +10002,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10054,7 +10049,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10064,14 +10059,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44732</v>
+        <v>45636</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10085,11 +10080,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>39</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10132,7 +10127,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10146,10 +10141,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45281</v>
+        <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10162,7 +10157,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10205,7 +10200,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45730</v>
+        <v>45463</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10234,8 +10229,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>7.9</v>
+        <v>30.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45079</v>
+        <v>45614</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10307,13 +10307,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10356,7 +10351,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38823-2026</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10366,14 +10361,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46286</v>
+        <v>45079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10387,11 +10382,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10434,7 +10429,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10448,10 +10443,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45281</v>
+        <v>45468</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10464,7 +10459,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13.4</v>
+        <v>6.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10507,7 +10502,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10517,14 +10512,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45636</v>
+        <v>46181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10536,13 +10531,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.5</v>
+        <v>16.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10585,7 +10575,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39456-2026</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10595,14 +10585,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46288</v>
+        <v>46188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10614,8 +10604,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>16.2</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10658,7 +10653,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10672,10 +10667,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45583</v>
+        <v>45467</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10688,7 +10683,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>17.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10731,7 +10726,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10741,14 +10736,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45250</v>
+        <v>46104</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10760,8 +10755,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>31.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45079</v>
+        <v>45281</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10833,13 +10833,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>29</v>
+        <v>43.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10882,7 +10877,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10896,10 +10891,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45825</v>
+        <v>46198</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10917,7 +10912,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>23.7</v>
+        <v>18</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10960,7 +10955,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10974,10 +10969,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46104</v>
+        <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10991,11 +10986,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>31.7</v>
+        <v>11.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11038,7 +11033,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11052,10 +11047,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45621</v>
+        <v>46197</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11067,8 +11062,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>11.3</v>
+        <v>14.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11111,7 +11111,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44701</v>
+        <v>45730</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>20.3</v>
+        <v>4.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11184,7 +11184,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11194,14 +11194,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45469</v>
+        <v>46252</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11213,8 +11213,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11257,7 +11262,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11271,10 +11276,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46139</v>
+        <v>45530</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11287,7 +11292,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>20.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11330,7 +11335,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11340,14 +11345,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46139</v>
+        <v>46189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11359,8 +11364,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11403,7 +11413,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11417,10 +11427,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46139</v>
+        <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11432,8 +11442,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3.1</v>
+        <v>17.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11476,7 +11491,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11490,10 +11505,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45469</v>
+        <v>46198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11505,8 +11520,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>8.199999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11549,7 +11569,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11559,14 +11579,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44830</v>
+        <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11580,11 +11600,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11627,7 +11647,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11641,10 +11661,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44741</v>
+        <v>45153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11656,8 +11676,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11700,7 +11725,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11714,10 +11739,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11729,8 +11754,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>7.7</v>
+        <v>22.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11773,7 +11803,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11787,10 +11817,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45825</v>
+        <v>45281</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11802,13 +11832,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>25.1</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11851,7 +11876,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11861,14 +11886,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46162</v>
+        <v>46266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11880,8 +11905,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11924,7 +11954,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11938,10 +11968,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45468</v>
+        <v>46028</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11954,7 +11984,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.9</v>
+        <v>19.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11997,7 +12027,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12011,10 +12041,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45614</v>
+        <v>45625</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12027,7 +12057,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12070,7 +12100,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12084,10 +12114,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46181</v>
+        <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12099,8 +12129,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>16.9</v>
+        <v>13.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12143,7 +12178,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12153,14 +12188,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46188</v>
+        <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12172,13 +12207,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12221,7 +12251,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12235,10 +12265,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46197</v>
+        <v>45625</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12250,13 +12280,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>14.2</v>
+        <v>7.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12299,7 +12324,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12313,10 +12338,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46198</v>
+        <v>45625</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12328,13 +12353,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12377,7 +12397,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12391,10 +12411,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46198</v>
+        <v>44830</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12408,11 +12428,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12455,7 +12475,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12469,10 +12489,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46252</v>
+        <v>44479</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12484,13 +12504,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>19.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12533,7 +12548,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 38823-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12547,10 +12562,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46189</v>
+        <v>46286</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12564,11 +12579,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12611,7 +12626,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 39456-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12625,10 +12640,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46198</v>
+        <v>46288</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12640,13 +12655,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>13.3</v>
+        <v>16.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12689,7 +12699,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12699,14 +12709,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46197</v>
+        <v>44833</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12718,13 +12728,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.8</v>
+        <v>24.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12767,7 +12772,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46198</v>
+        <v>44833</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12796,13 +12801,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>17.2</v>
+        <v>23.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12845,7 +12845,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12859,10 +12859,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46197</v>
+        <v>45079</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12876,11 +12876,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12933,14 +12933,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46266</v>
+        <v>45832</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12952,13 +12952,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13001,7 +12996,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13015,10 +13010,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46269</v>
+        <v>44732</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13032,11 +13027,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>13.9</v>
+        <v>39</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13079,7 +13074,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13093,10 +13088,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46028</v>
+        <v>45825</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13108,8 +13103,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13169,7 +13169,7 @@
         <v>45013</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE139"/>
+  <dimension ref="A1:AE137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24892-2026</t>
+          <t>A 2256-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46174</v>
+        <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3124,175 +3124,51 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>19.7</v>
+        <v>17.9</v>
       </c>
       <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13</v>
-      </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Gräddporing
-Blanksvart spiklav
-Dvärgbägarlav
-Grå blåbärsfältmätare
-Mörk kolflarnlav
-Talltagel
-Talltita
-Vedflamlav
-Vedskivlav
-Vitplätt
-Älg
-Tjäder
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 24892-2026 artfynd.xlsx", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 24892-2026 karta.png", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 24892-2026 georefererad karta.tif", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 24892-2026 FSC-klagomål.docx", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 24892-2026 FSC-klagomål mail.docx", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 24892-2026 tillsynsbegäran.docx", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 24892-2026 tillsynsbegäran mail.docx", "A 24892-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 24892-2026 prioriterade fågelarter.docx", "A 24892-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 2256-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45671</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>31</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hökuggla
 Månlåsbräken
@@ -3307,43 +3183,162 @@
 Fjällummer</t>
         </is>
       </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 2256-2025 artfynd.xlsx", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 2256-2025 karta.png", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 2256-2025 georefererad karta.tif", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 2256-2025 FSC-klagomål.docx", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 2256-2025 FSC-klagomål mail.docx", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 2256-2025 tillsynsbegäran.docx", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 2256-2025 tillsynsbegäran mail.docx", "A 2256-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 2256-2025 prioriterade fågelarter.docx", "A 2256-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
+        <v>16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 2256-2025 artfynd.xlsx", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 2256-2025 karta.png", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 2256-2025 georefererad karta.tif", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 2256-2025 FSC-klagomål.docx", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 2256-2025 FSC-klagomål mail.docx", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 2256-2025 tillsynsbegäran.docx", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 2256-2025 tillsynsbegäran mail.docx", "A 2256-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 2256-2025 prioriterade fågelarter.docx", "A 2256-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45030-2023</t>
+          <t>A 1479-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3357,10 +3352,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45190</v>
+        <v>46033</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3378,19 +3373,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3402,21 +3397,140 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>14</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3430,230 +3544,234 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45031-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45190</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
-        <v>16</v>
-      </c>
-      <c r="U23" t="n">
-        <v>14</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
-Sprickporing
-Vitskaftad svartspik
+Ostticka
 Gammelgransskål
-Rosenticka
+Harticka
+Knottrig blåslav
+Tretåig hackspett
 Ullticka
 Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 45417-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45576</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>11.5</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>10</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>10</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>20</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>20</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Dvärgbägarlav
@@ -3667,166 +3785,43 @@
 Vedtrappmossa</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>13</v>
-      </c>
-      <c r="U25" t="n">
-        <v>11</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1479-2026</t>
+          <t>A 31143-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3840,10 +3835,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46033</v>
+        <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3855,25 +3850,20 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>16.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3885,135 +3875,21 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Sprickporing
-Vitskaftad svartspik
-Gammelgransskål
-Rosenticka
-Ullticka
-Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31143-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45831</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>9</v>
-      </c>
-      <c r="T27" t="n">
-        <v>25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>25</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4026,43 +3902,159 @@
 Vitgrynig nållav</t>
         </is>
       </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 31143-2025 artfynd.xlsx", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 31143-2025 karta.png", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 31143-2025 georefererad karta.tif", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 31143-2025 FSC-klagomål.docx", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 31143-2025 FSC-klagomål mail.docx", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 31143-2025 tillsynsbegäran.docx", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 31143-2025 tillsynsbegäran mail.docx", "A 31143-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 31143-2025 prioriterade fågelarter.docx", "A 31143-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tajgaskinn
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Ullticka
+Blodticka
+Tjäder</t>
+        </is>
+      </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 31143-2025 artfynd.xlsx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 31143-2025 karta.png", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 31143-2025 georefererad karta.tif", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 31143-2025 FSC-klagomål.docx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 31143-2025 FSC-klagomål mail.docx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 31143-2025 tillsynsbegäran.docx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 31143-2025 tillsynsbegäran mail.docx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 31143-2025 prioriterade fågelarter.docx", "A 31143-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45032-2023</t>
+          <t>A 28351-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4076,10 +4068,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45190</v>
+        <v>45818</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4091,16 +4083,11 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -4130,12 +4117,129 @@
         <v>8</v>
       </c>
       <c r="T28" t="n">
+        <v>13</v>
+      </c>
+      <c r="U28" t="n">
+        <v>13</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
         <v>9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>7</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4147,111 +4251,111 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48673-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>32.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -4263,155 +4367,43 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>13</v>
-      </c>
-      <c r="U30" t="n">
-        <v>13</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 1478-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4425,10 +4417,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45327</v>
+        <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4440,17 +4432,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
@@ -4465,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
         <v>2</v>
@@ -4474,133 +4471,12 @@
         <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tajgaskinn
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Ullticka
-Blodticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>9</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4612,116 +4488,116 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1478-2026 karta.png", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1478-2026 georefererad karta.tif", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1478-2026 FSC-klagomål.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1478-2026 FSC-klagomål mail.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1478-2026 tillsynsbegäran.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1478-2026 tillsynsbegäran mail.docx", "A 1478-2026")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1478-2026 prioriterade fågelarter.docx", "A 1478-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 49079-2025</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>45937</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I32" t="n">
         <v>24.7</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J32" t="n">
         <v>5</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S32" t="n">
         <v>6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T32" t="n">
         <v>6</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Lunglav
@@ -4731,32 +4607,150 @@
 Revlummer</t>
         </is>
       </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 49079-2025 artfynd.xlsx", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 49079-2025 karta.png", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 49079-2025 georefererad karta.tif", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 49079-2025 FSC-klagomål.docx", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 49079-2025 FSC-klagomål mail.docx", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 49079-2025 tillsynsbegäran.docx", "A 49079-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 49079-2025 tillsynsbegäran mail.docx", "A 49079-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 25229-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Gammelgransskål
+Rosenticka
+Rödbrun blekspik
+Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 49079-2025 artfynd.xlsx", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 49079-2025 karta.png", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 49079-2025 georefererad karta.tif", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 49079-2025 FSC-klagomål.docx", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 49079-2025 FSC-klagomål mail.docx", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 49079-2025 tillsynsbegäran.docx", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 49079-2025 tillsynsbegäran mail.docx", "A 49079-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
         <v/>
       </c>
     </row>
@@ -4780,7 +4774,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4872,7 +4866,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25229-2023</t>
+          <t>A 12403-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4886,10 +4880,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45079</v>
+        <v>45730</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4901,13 +4895,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>18.2</v>
+        <v>10.1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4916,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -4931,59 +4920,58 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Ostticka
-Gammelgransskål
-Rosenticka
-Rödbrun blekspik
-Tretåig hackspett</t>
+          <t>Garnlav
+Harticka
+Tretåig hackspett
+Vedskivlav</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
       <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
         <v/>
       </c>
     </row>
@@ -5007,7 +4995,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5098,7 +5086,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12403-2025</t>
+          <t>A 26143-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5112,10 +5100,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45730</v>
+        <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5128,82 +5116,77 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.1</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4</v>
-      </c>
       <c r="T37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Harticka
-Tretåig hackspett
-Vedskivlav</t>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
@@ -5227,7 +5210,7 @@
         <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5321,7 +5304,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26143-2024</t>
+          <t>A 10525-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5335,10 +5318,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45467</v>
+        <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5351,16 +5334,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.1</v>
+        <v>15.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5375,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5384,263 +5367,266 @@
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 10525-2024</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>45366</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Spindelblomster
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>A 36564-2026</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="E40" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I40" t="n">
         <v>21.5</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2</v>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>3</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T40" t="n">
         <v>5</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Blå taggsvamp
 Kolflarnlav
 Stuplav</t>
         </is>
       </c>
+      <c r="W40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="Y40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+      <c r="AD40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A 45324-2022</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>44841</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Bergand
+Sångsvan</t>
+        </is>
+      </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 36564-2026 artfynd.xlsx", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 36564-2026 karta.png", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 36564-2026 georefererad karta.tif", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 36564-2026 FSC-klagomål.docx", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 36564-2026 FSC-klagomål mail.docx", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 36564-2026 tillsynsbegäran.docx", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 36564-2026 tillsynsbegäran mail.docx", "A 36564-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
         <v/>
       </c>
     </row>
@@ -5664,7 +5650,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5758,7 +5744,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45324-2022</t>
+          <t>A 12789-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5772,10 +5758,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44841</v>
+        <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5787,20 +5773,25 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>23.2</v>
+        <v>56.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5815,60 +5806,55 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>2</v>
-      </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Bergand
-Sångsvan</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12789-2022 artfynd.xlsx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12789-2022 karta.png", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12789-2022 georefererad karta.tif", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12789-2022 FSC-klagomål.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12789-2022 FSC-klagomål mail.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12789-2022 tillsynsbegäran.docx", "A 12789-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12789-2022 tillsynsbegäran mail.docx", "A 12789-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12789-2022</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5882,10 +5868,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44642</v>
+        <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5897,22 +5883,17 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>56.1</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5927,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5939,46 +5920,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12789-2022 artfynd.xlsx", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12789-2022 karta.png", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12789-2022 georefererad karta.tif", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12789-2022 FSC-klagomål.docx", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12789-2022 FSC-klagomål mail.docx", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12789-2022 tillsynsbegäran.docx", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12789-2022 tillsynsbegäran mail.docx", "A 12789-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5992,10 +5973,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45777</v>
+        <v>45034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6008,10 +5989,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.6</v>
+        <v>18.8</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -6048,42 +6029,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6097,10 +6082,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6112,8 +6097,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6149,46 +6139,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6202,10 +6192,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45034</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6218,10 +6208,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>18.8</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6258,46 +6248,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 66844-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6311,10 +6297,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45079</v>
+        <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6326,19 +6312,14 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>44.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6362,52 +6343,20 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
-        <v/>
-      </c>
+      <c r="V48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 66844-2021</t>
+          <t>A 56274-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6421,10 +6370,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44520</v>
+        <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6437,7 +6386,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>44.8</v>
+        <v>6.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6480,7 +6429,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56274-2021</t>
+          <t>A 56275-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6497,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6510,7 +6459,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.6</v>
+        <v>16.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6553,7 +6502,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56275-2021</t>
+          <t>A 56277-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6563,14 +6512,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6583,7 +6532,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>16.2</v>
+        <v>19.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6626,7 +6575,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56277-2021</t>
+          <t>A 44751-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6636,14 +6585,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44479</v>
+        <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6655,8 +6604,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>19.4</v>
+        <v>26.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6699,7 +6653,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44751-2022</t>
+          <t>A 56278-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6713,10 +6667,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44840</v>
+        <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6728,13 +6682,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>26.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6777,7 +6726,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56278-2021</t>
+          <t>A 52573-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6791,10 +6740,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44479</v>
+        <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6807,7 +6756,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6850,7 +6799,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52573-2022</t>
+          <t>A 19620-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6860,14 +6809,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44874</v>
+        <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6879,8 +6828,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6923,7 +6877,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19620-2022</t>
+          <t>A 72279-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6937,10 +6891,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44694</v>
+        <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6952,13 +6906,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7001,7 +6950,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 72279-2021</t>
+          <t>A 58879-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7011,14 +6960,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44543</v>
+        <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7031,7 +6980,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7074,7 +7023,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58879-2021</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7088,10 +7037,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44489</v>
+        <v>45625</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7104,7 +7053,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7147,7 +7096,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7161,10 +7110,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45583</v>
+        <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7177,7 +7126,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>18.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7220,7 +7169,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7234,10 +7183,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45618</v>
+        <v>45467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7250,7 +7199,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7293,7 +7242,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7303,14 +7252,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44475</v>
+        <v>45530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7322,13 +7271,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>20.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7371,7 +7315,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7385,10 +7329,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45621</v>
+        <v>45859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7345,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7444,7 +7388,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7454,14 +7398,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45187</v>
+        <v>45664</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7473,8 +7417,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7517,7 +7466,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7527,14 +7476,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45250</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7547,7 +7496,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>43.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7590,7 +7539,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7604,10 +7553,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45315</v>
+        <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7620,7 +7569,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7663,7 +7612,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7673,14 +7622,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45664</v>
+        <v>45153</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7694,11 +7643,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>16.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7741,7 +7690,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7755,10 +7704,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45455</v>
+        <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7770,13 +7719,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7819,7 +7763,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7833,10 +7777,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44473</v>
+        <v>45730</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7849,7 +7793,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7892,7 +7836,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7906,10 +7850,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45859</v>
+        <v>45079</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7921,8 +7865,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7965,7 +7914,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7979,10 +7928,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46139</v>
+        <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7995,7 +7944,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -8038,7 +7987,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8048,14 +7997,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45903</v>
+        <v>45636</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8067,8 +8016,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8111,7 +8065,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8125,10 +8079,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45905</v>
+        <v>45455</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8140,8 +8094,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8184,7 +8143,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42526-2025</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8198,10 +8157,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45905</v>
+        <v>44833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8214,7 +8173,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>12.5</v>
+        <v>24.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8257,7 +8216,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8271,10 +8230,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46139</v>
+        <v>44833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8287,7 +8246,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>23.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8330,7 +8289,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8340,14 +8299,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45216</v>
+        <v>45937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8359,8 +8318,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>6.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8403,7 +8367,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8413,14 +8377,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44701</v>
+        <v>44475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8432,8 +8396,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>20.3</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8476,7 +8445,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8486,14 +8455,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45937</v>
+        <v>45079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8507,11 +8476,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.5</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8554,7 +8523,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8568,10 +8537,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8583,8 +8552,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>31.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8627,7 +8601,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8641,10 +8615,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45469</v>
+        <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8657,7 +8631,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8700,7 +8674,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8714,10 +8688,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45469</v>
+        <v>45034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8729,8 +8703,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>8.199999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8773,7 +8752,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8783,14 +8762,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45281</v>
+        <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8802,8 +8781,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8846,7 +8830,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8860,10 +8844,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45845</v>
+        <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8876,7 +8860,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8919,7 +8903,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8933,10 +8917,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44735</v>
+        <v>45649</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8954,7 +8938,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8997,7 +8981,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9011,10 +8995,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45034</v>
+        <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9026,13 +9010,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>20.3</v>
+        <v>11.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9075,7 +9054,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9089,10 +9068,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44741</v>
+        <v>45999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9105,7 +9084,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9148,7 +9127,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9162,10 +9141,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45993</v>
+        <v>45469</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9178,7 +9157,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9221,7 +9200,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9235,10 +9214,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45999</v>
+        <v>46139</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9251,7 +9230,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9294,7 +9273,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9308,10 +9287,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45999</v>
+        <v>46139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9324,7 +9303,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9367,7 +9346,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9377,14 +9356,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45183</v>
+        <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9396,13 +9375,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9445,7 +9419,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9459,10 +9433,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45625</v>
+        <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9475,7 +9449,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.5</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9518,7 +9492,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9532,10 +9506,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45825</v>
+        <v>44874</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9547,13 +9521,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>25.1</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9596,7 +9565,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9610,10 +9579,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46162</v>
+        <v>45832</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9626,7 +9595,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9669,7 +9638,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9683,10 +9652,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46162</v>
+        <v>44741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9699,7 +9668,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>15.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9742,7 +9711,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9752,14 +9721,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45649</v>
+        <v>45079</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9777,7 +9746,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>22.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9820,7 +9789,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9830,14 +9799,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44735</v>
+        <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9849,13 +9818,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9898,7 +9862,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9912,10 +9876,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45730</v>
+        <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9928,7 +9892,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9971,7 +9935,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9985,10 +9949,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45079</v>
+        <v>45825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10002,11 +9966,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>25.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10049,7 +10013,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10059,14 +10023,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45636</v>
+        <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10080,11 +10044,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.5</v>
+        <v>39</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10127,7 +10091,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10141,10 +10105,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44874</v>
+        <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10157,7 +10121,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10200,7 +10164,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10214,10 +10178,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45463</v>
+        <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10229,13 +10193,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>30.7</v>
+        <v>9.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10278,7 +10237,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10292,10 +10251,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45614</v>
+        <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10307,8 +10266,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>23.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10351,7 +10315,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10365,10 +10329,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45079</v>
+        <v>45463</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10382,11 +10346,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>29</v>
+        <v>30.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10446,7 +10410,7 @@
         <v>45468</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10502,7 +10466,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10516,10 +10480,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46181</v>
+        <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10532,7 +10496,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10575,7 +10539,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10585,14 +10549,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10604,13 +10568,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>16.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10653,7 +10612,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10663,14 +10622,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45467</v>
+        <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10682,8 +10641,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>17.2</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10726,7 +10690,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10740,10 +10704,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46104</v>
+        <v>46197</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10757,11 +10721,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>31.7</v>
+        <v>14.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10804,7 +10768,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10818,10 +10782,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45281</v>
+        <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10834,7 +10798,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>43.6</v>
+        <v>11.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10877,7 +10841,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10891,10 +10855,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46198</v>
+        <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10906,13 +10870,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>18</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10955,7 +10914,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10972,7 +10931,7 @@
         <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10990,7 +10949,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11033,7 +10992,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11047,10 +11006,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11068,7 +11027,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>14.2</v>
+        <v>11.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11111,7 +11070,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11121,14 +11080,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45730</v>
+        <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11140,8 +11099,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11184,7 +11148,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11194,14 +11158,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46252</v>
+        <v>45625</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11213,13 +11177,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11262,7 +11221,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11276,10 +11235,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45530</v>
+        <v>45625</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11292,7 +11251,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>20.1</v>
+        <v>7.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11352,7 +11311,7 @@
         <v>46189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11413,7 +11372,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11430,7 +11389,7 @@
         <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11448,7 +11407,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>17.2</v>
+        <v>13.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11491,7 +11450,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11505,10 +11464,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46198</v>
+        <v>45730</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11520,13 +11479,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>13.3</v>
+        <v>4.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11586,7 +11540,7 @@
         <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11647,7 +11601,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11661,10 +11615,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45153</v>
+        <v>46198</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11678,11 +11632,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11742,7 +11696,7 @@
         <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11803,7 +11757,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11813,14 +11767,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45281</v>
+        <v>44735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11832,8 +11786,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11893,7 +11852,7 @@
         <v>46266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11954,7 +11913,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11964,14 +11923,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46028</v>
+        <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11983,8 +11942,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12027,7 +11991,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12041,10 +12005,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45625</v>
+        <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12056,8 +12020,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12100,7 +12069,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12114,10 +12083,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46269</v>
+        <v>46028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12129,13 +12098,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>13.9</v>
+        <v>19.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12178,7 +12142,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12192,10 +12156,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45625</v>
+        <v>45281</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12208,7 +12172,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12251,7 +12215,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12265,10 +12229,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45625</v>
+        <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12281,7 +12245,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.5</v>
+        <v>13.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12324,7 +12288,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12338,10 +12302,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45625</v>
+        <v>45583</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12354,7 +12318,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12397,7 +12361,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 39456-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12411,10 +12375,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44830</v>
+        <v>46288</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12426,13 +12390,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6.5</v>
+        <v>16.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12475,7 +12434,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12485,14 +12444,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44479</v>
+        <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12505,7 +12464,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>19.8</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12565,7 +12524,7 @@
         <v>46286</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12626,7 +12585,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 39456-2026</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12640,10 +12599,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46288</v>
+        <v>46139</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12656,7 +12615,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12699,7 +12658,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12713,10 +12672,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44833</v>
+        <v>45621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12729,7 +12688,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>24.6</v>
+        <v>11.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12772,7 +12731,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12786,10 +12745,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44833</v>
+        <v>44701</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12802,7 +12761,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>23.2</v>
+        <v>20.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12845,7 +12804,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12859,10 +12818,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45079</v>
+        <v>44830</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12876,11 +12835,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>22.7</v>
+        <v>6.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12923,7 +12882,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12933,14 +12892,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45832</v>
+        <v>44479</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12953,7 +12912,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.3</v>
+        <v>19.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12993,27 +12952,27 @@
       </c>
       <c r="V136" s="2" t="inlineStr"/>
     </row>
-    <row r="137" ht="15" customHeight="1">
+    <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>S 1086-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44732</v>
+        <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13027,11 +12986,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>39</v>
+        <v>24.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13070,162 +13029,6 @@
         <v>0</v>
       </c>
       <c r="V137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>A 29662-2025</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E138" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>S 1086-2023</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D139" s="1" t="n">
-        <v>45013</v>
-      </c>
-      <c r="E139" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="I139" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>46033</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46033</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>45576</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45818</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45203</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>45730</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45625</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45664</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45153</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45730</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45079</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45636</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45455</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45649</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>45999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45469</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>46139</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>46139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44874</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45832</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45079</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45463</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45468</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46197</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45625</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45625</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>46189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45730</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>46198</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>46266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45281</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45583</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46288</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46286</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46139</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44701</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44830</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44479</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>46033</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46033</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>45576</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45818</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45203</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>45730</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45625</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45664</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45153</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45730</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45079</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45636</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45455</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45649</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>45999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45469</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>46139</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>46139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44874</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45832</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45079</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45315</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45463</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45468</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>46181</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46197</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>46198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45625</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45625</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>46189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45730</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>46198</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>46266</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45281</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45583</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46288</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46286</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46139</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44701</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44830</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44479</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45031-2023</t>
+          <t>A 45030-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3236,7 +3236,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3278,21 +3278,144 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>14</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3306,112 +3429,353 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 1479-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M25" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R25" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U25" t="n">
         <v>14</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3425,396 +3789,32 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>13</v>
-      </c>
-      <c r="U23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13</v>
-      </c>
-      <c r="U24" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>10</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20</v>
-      </c>
-      <c r="U25" t="n">
-        <v>20</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
         <v/>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4544-2024</t>
+          <t>A 28351-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45327</v>
+        <v>45818</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -4001,12 +4001,361 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>13</v>
+      </c>
+      <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Ullticka
+Vedflamlav
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>7</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 48673-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 4544-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
         <v>17</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Tajgaskinn
@@ -4018,228 +4367,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 28351-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="D31" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
-        <v>13</v>
-      </c>
-      <c r="U28" t="n">
-        <v>13</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
-Garnlav
-Blanksvart spiklav
-Dropptaggsvamp
-Dvärgbägarlav
-Ullticka
-Vedflamlav
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4251,243 +4488,6 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
@@ -4541,7 +4541,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25229-2023</t>
+          <t>A 59199-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45079</v>
+        <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4668,16 +4668,11 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4707,12 +4702,126 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
+        <v>9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Gammelgransskål
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 25229-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Gammelgransskål
@@ -4721,152 +4830,43 @@
 Tretåig hackspett</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 59199-2021</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>44490</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Gammelgransskål
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12403-2025</t>
+          <t>A 64803-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>43</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4923,18 +4923,126 @@
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
       </c>
       <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Gullmurkling
+Lunglav
+Rosenticka
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 12403-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45730</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="n">
         <v>9</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>9</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -4942,151 +5050,43 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 64803-2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>43</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Gullmurkling
-Lunglav
-Rosenticka
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26143-2024</t>
+          <t>A 15171-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45467</v>
+        <v>44658</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>48</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5152,152 +5152,152 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Knottrig blåslav
 Vedticka</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15171-2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>44658</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>48</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Tretåig hackspett
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
         <v/>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45324-2022</t>
+          <t>A 41375-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44841</v>
+        <v>45559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5552,20 +5552,25 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>23.2</v>
+        <v>5.9</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5577,167 +5582,162 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Brudsporre</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 45324-2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>44841</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Bergand
 Sångsvan</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 41375-2024</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>45559</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Brudsporre</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
         <v/>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 17549-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46076</v>
+        <v>45034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5884,17 +5884,17 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>18.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5920,46 +5920,50 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17549-2023</t>
+          <t>A 25279-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5973,10 +5977,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45034</v>
+        <v>45079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5988,17 +5992,22 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>18.8</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6013,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6029,46 +6038,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 17549-2023 artfynd.xlsx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 17549-2023 karta.png", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 17549-2023 georefererad karta.tif", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 17549-2023 FSC-klagomål.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 17549-2023 FSC-klagomål mail.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 17549-2023 tillsynsbegäran.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 17549-2023 tillsynsbegäran mail.docx", "A 17549-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 17549-2023 prioriterade fågelarter.docx", "A 17549-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25279-2023</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6082,10 +6087,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45079</v>
+        <v>45777</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6097,37 +6102,32 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.9</v>
+        <v>10.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6143,42 +6143,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25279-2023 artfynd.xlsx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25279-2023 karta.png", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25279-2023 georefererad karta.tif", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25279-2023 FSC-klagomål.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25279-2023 FSC-klagomål mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25279-2023 tillsynsbegäran.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25279-2023 tillsynsbegäran mail.docx", "A 25279-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6244,39 +6244,39 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45625</v>
+        <v>45583</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.2</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>18.3</v>
+        <v>11.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45467</v>
+        <v>45618</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7252,14 +7252,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45530</v>
+        <v>44475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7271,8 +7271,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>20.1</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7315,7 +7320,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7329,10 +7334,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45859</v>
+        <v>45187</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7345,7 +7350,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7388,7 +7393,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7398,14 +7403,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45664</v>
+        <v>45859</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7417,13 +7422,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>43.6</v>
+        <v>24.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45903</v>
+        <v>44833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>23.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45153</v>
+        <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7641,13 +7641,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>16.9</v>
+        <v>10</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7707,7 +7702,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7763,7 +7758,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7773,14 +7768,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45730</v>
+        <v>45250</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7793,7 +7788,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.9</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7836,7 +7831,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45079</v>
+        <v>45216</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7865,13 +7860,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7914,7 +7904,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7928,10 +7918,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45216</v>
+        <v>45079</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7943,8 +7933,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>22.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7987,7 +7982,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7997,14 +7992,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45636</v>
+        <v>45832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8016,13 +8011,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8065,7 +8055,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8079,10 +8069,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45455</v>
+        <v>45315</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8094,13 +8084,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>9.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8143,7 +8128,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8157,10 +8142,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44833</v>
+        <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8172,8 +8157,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>24.6</v>
+        <v>39</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8216,7 +8206,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8226,14 +8216,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44833</v>
+        <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8245,8 +8235,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>23.2</v>
+        <v>6.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8289,7 +8284,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45937</v>
+        <v>45664</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8320,11 +8315,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8367,7 +8362,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8377,14 +8372,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44475</v>
+        <v>45825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8398,11 +8393,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>23.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45079</v>
+        <v>45455</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8476,11 +8471,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8523,7 +8518,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8537,10 +8532,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46104</v>
+        <v>45845</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8552,13 +8547,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>31.7</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8601,7 +8591,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8615,10 +8605,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45845</v>
+        <v>45034</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8630,8 +8620,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>20.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8674,7 +8669,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8688,10 +8683,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45034</v>
+        <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8703,13 +8698,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>20.3</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8752,7 +8742,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8762,14 +8752,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44735</v>
+        <v>45730</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8781,13 +8771,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>7.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8830,7 +8815,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8844,10 +8829,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8860,7 +8845,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8903,7 +8888,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8913,14 +8898,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45649</v>
+        <v>45999</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8932,13 +8917,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8981,7 +8961,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8995,10 +8975,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45999</v>
+        <v>44473</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9011,7 +8991,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>11.3</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9054,7 +9034,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9068,10 +9048,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45999</v>
+        <v>45079</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9083,8 +9063,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9127,7 +9112,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9141,10 +9126,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45469</v>
+        <v>44701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9157,7 +9142,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>20.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9200,7 +9185,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9210,14 +9195,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46139</v>
+        <v>45636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9229,8 +9214,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9273,7 +9263,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9287,10 +9277,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46139</v>
+        <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9302,8 +9292,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9346,7 +9341,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9360,10 +9355,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45469</v>
+        <v>46104</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9375,8 +9370,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>8.199999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45187</v>
+        <v>45281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>13.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9492,7 +9492,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9502,14 +9502,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44874</v>
+        <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9521,8 +9521,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9565,7 +9570,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9579,10 +9584,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45832</v>
+        <v>46139</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9595,7 +9600,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9638,7 +9643,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44741</v>
+        <v>46139</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9668,7 +9673,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>15.6</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9711,7 +9716,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9721,14 +9726,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45079</v>
+        <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9742,11 +9747,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>22.7</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9789,7 +9794,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9803,10 +9808,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44473</v>
+        <v>45625</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9819,7 +9824,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9862,7 +9867,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9872,14 +9877,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46162</v>
+        <v>45649</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9891,8 +9896,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>7.7</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9935,7 +9945,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9949,10 +9959,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45825</v>
+        <v>45469</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9964,13 +9974,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>25.1</v>
+        <v>7.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10013,7 +10018,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10027,10 +10032,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44732</v>
+        <v>45469</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10042,13 +10047,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>39</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10101,14 +10101,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46162</v>
+        <v>44735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10120,8 +10120,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10164,7 +10169,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10178,10 +10183,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45315</v>
+        <v>44741</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10194,7 +10199,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>9.1</v>
+        <v>15.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10237,7 +10242,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10254,7 +10259,7 @@
         <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10272,7 +10277,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>23.7</v>
+        <v>25.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10315,7 +10320,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10329,10 +10334,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45463</v>
+        <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10344,13 +10349,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>30.7</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10393,7 +10393,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45468</v>
+        <v>46162</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10466,7 +10466,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45614</v>
+        <v>44874</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10539,7 +10539,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10553,10 +10553,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46181</v>
+        <v>45463</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10568,8 +10568,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>16.9</v>
+        <v>30.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10612,7 +10617,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10622,14 +10627,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46188</v>
+        <v>45467</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10641,13 +10646,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>17.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10690,7 +10690,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10704,10 +10704,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46197</v>
+        <v>45614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10719,13 +10719,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>14.2</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10768,7 +10763,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10782,10 +10777,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45625</v>
+        <v>45281</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10798,7 +10793,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.5</v>
+        <v>43.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10841,7 +10836,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 26479-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10855,10 +10850,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45625</v>
+        <v>45468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10871,7 +10866,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10914,7 +10909,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10928,10 +10923,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46198</v>
+        <v>46181</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10943,13 +10938,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>18</v>
+        <v>16.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10992,7 +10982,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11002,14 +10992,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11023,11 +11013,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11070,7 +11060,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11080,14 +11070,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46252</v>
+        <v>45730</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11099,13 +11089,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11148,7 +11133,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11162,10 +11147,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45625</v>
+        <v>46198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11177,8 +11162,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11221,7 +11211,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11235,10 +11225,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45625</v>
+        <v>46198</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11250,8 +11240,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11294,7 +11289,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11304,14 +11299,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11325,11 +11320,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.1</v>
+        <v>14.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11372,7 +11367,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11386,10 +11381,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46198</v>
+        <v>45530</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11401,13 +11396,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>13.3</v>
+        <v>20.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11450,7 +11440,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11460,14 +11450,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45730</v>
+        <v>46252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11479,8 +11469,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11523,7 +11518,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11537,10 +11532,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46197</v>
+        <v>46189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11554,11 +11549,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11601,7 +11596,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11615,10 +11610,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46198</v>
+        <v>45153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11632,11 +11627,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11679,7 +11674,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11693,10 +11688,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11714,7 +11709,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>22.9</v>
+        <v>17.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11757,7 +11752,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11767,14 +11762,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44735</v>
+        <v>46198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11788,11 +11783,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11835,7 +11830,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11849,10 +11844,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46266</v>
+        <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11866,11 +11861,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11913,7 +11908,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11923,14 +11918,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45183</v>
+        <v>46197</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11948,7 +11943,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>22.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11991,7 +11986,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12005,10 +12000,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46269</v>
+        <v>45281</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12020,13 +12015,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>13.9</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12069,7 +12059,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 390-2026</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12079,14 +12069,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46028</v>
+        <v>46266</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12098,8 +12088,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12142,7 +12137,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12156,10 +12151,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45281</v>
+        <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12172,7 +12167,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12215,7 +12210,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12229,10 +12224,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45281</v>
+        <v>45625</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12245,7 +12240,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>13.4</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12288,7 +12283,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 390-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45583</v>
+        <v>46028</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12318,7 +12313,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.6</v>
+        <v>19.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12361,7 +12356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39456-2026</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12375,10 +12370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46288</v>
+        <v>46269</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12390,8 +12385,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>16.2</v>
+        <v>13.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12434,7 +12434,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12444,14 +12444,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45250</v>
+        <v>45625</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12507,7 +12507,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38823-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12517,14 +12517,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46286</v>
+        <v>45625</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12536,13 +12536,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12585,7 +12580,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12599,10 +12594,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46139</v>
+        <v>44830</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12614,8 +12609,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12658,7 +12658,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12668,14 +12668,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45621</v>
+        <v>44479</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>11.3</v>
+        <v>19.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12731,7 +12731,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 39456-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12745,10 +12745,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44701</v>
+        <v>46288</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>20.3</v>
+        <v>16.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12804,7 +12804,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 38823-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12814,14 +12814,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44830</v>
+        <v>46286</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12835,11 +12835,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12882,7 +12882,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12892,14 +12892,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44479</v>
+        <v>46139</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>19.8</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12972,7 +12972,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45030-2023</t>
+          <t>A 45031-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3236,7 +3236,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3278,21 +3278,140 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>14</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Sprickporing
+Vitskaftad svartspik
+Gammelgransskål
+Rosenticka
+Ullticka
+Vitgrynig nållav
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45030-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>11</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3306,116 +3425,116 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45031-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1479-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>4</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>8</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>14</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3429,107 +3548,230 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 45417-2024</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45576</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>11.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>10</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>20</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>20</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Dvärgbägarlav
@@ -3543,278 +3785,36 @@
 Vedtrappmossa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13</v>
-      </c>
-      <c r="U24" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 1479-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>16</v>
-      </c>
-      <c r="U25" t="n">
-        <v>14</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Sprickporing
-Vitskaftad svartspik
-Gammelgransskål
-Rosenticka
-Ullticka
-Vitgrynig nållav
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28351-2025</t>
+          <t>A 4544-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45818</v>
+        <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3968,16 +3968,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -4001,12 +4001,128 @@
         <v>8</v>
       </c>
       <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tajgaskinn
+Knottrig blåslav
+Rosenticka
+Rynkskinn
+Ullticka
+Blodticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
         <v>13</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4018,112 +4134,112 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 45032-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>45190</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>6.3</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M29" t="n">
         <v>2</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>8</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>7</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4135,111 +4251,111 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 48673-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>32.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -4251,152 +4367,36 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 4544-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>17</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Tajgaskinn
-Knottrig blåslav
-Rosenticka
-Rynkskinn
-Ullticka
-Blodticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 4544-2024 artfynd.xlsx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 4544-2024 karta.png", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 4544-2024 georefererad karta.tif", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 4544-2024 FSC-klagomål.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 4544-2024 FSC-klagomål mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 4544-2024 tillsynsbegäran.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 4544-2024 tillsynsbegäran mail.docx", "A 4544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 4544-2024 prioriterade fågelarter.docx", "A 4544-2024")</f>
         <v/>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
         <v>46033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59199-2021</t>
+          <t>A 25229-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44490</v>
+        <v>45079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4668,11 +4668,16 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4702,12 +4707,125 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Gammelgransskål
+Rosenticka
+Rödbrun blekspik
+Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 59199-2021</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>44490</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
         <v>9</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Gammelgransskål
@@ -4716,157 +4834,39 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 25229-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45079</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Gammelgransskål
-Rosenticka
-Rödbrun blekspik
-Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64803-2023</t>
+          <t>A 12403-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45281</v>
+        <v>45730</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>43</v>
+        <v>10.1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4923,18 +4923,130 @@
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
       </c>
       <c r="T35" t="n">
+        <v>9</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Harticka
+Tretåig hackspett
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 64803-2023</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>43</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>4</v>
       </c>
-      <c r="U35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Gullmurkling
 Lunglav
@@ -4942,151 +5054,39 @@
 Ullticka</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 12403-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45730</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>9</v>
-      </c>
-      <c r="U36" t="n">
-        <v>9</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Harticka
-Tretåig hackspett
-Vedskivlav</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15171-2022</t>
+          <t>A 26143-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44658</v>
+        <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>48</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5152,152 +5152,152 @@
         <v>3</v>
       </c>
       <c r="U37" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Knottrig blåslav
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15171-2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>44658</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>48</v>
+      </c>
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Tretåig hackspett
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 26143-2024</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45467</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Knottrig blåslav
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
         <v>45366</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41375-2024</t>
+          <t>A 45324-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45559</v>
+        <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5552,26 +5552,21 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>23.2</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -5582,162 +5577,167 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Bergand
+Sångsvan</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 41375-2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45559</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
         <v>4</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Korallrot
 Brudsporre</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 45324-2022</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>44841</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Bergand
-Sångsvan</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
         <v/>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45777</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6103,16 +6103,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10.6</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6139,46 +6139,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46076</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6208,31 +6208,31 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6244,39 +6244,39 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44479</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44543</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46910-2024</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45583</v>
+        <v>45625</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>11.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55266-2024</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45618</v>
+        <v>45467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7252,14 +7252,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44475</v>
+        <v>45859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7271,13 +7271,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7320,7 +7315,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7334,10 +7329,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45187</v>
+        <v>45530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7350,7 +7345,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>20.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7393,7 +7388,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7407,10 +7402,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45859</v>
+        <v>45903</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7423,7 +7418,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7466,7 +7461,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7480,10 +7475,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44833</v>
+        <v>45905</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7496,7 +7491,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>24.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7556,7 +7551,7 @@
         <v>44833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7569,7 +7564,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7612,7 +7607,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7622,14 +7617,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45903</v>
+        <v>45664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7641,8 +7636,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45905</v>
+        <v>44833</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.199999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7758,7 +7758,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58370-2023</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7768,14 +7768,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45250</v>
+        <v>45281</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>43.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45216</v>
+        <v>45153</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7860,8 +7860,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>16.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7904,7 +7909,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7918,10 +7923,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45079</v>
+        <v>45832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7933,13 +7938,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>22.7</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45832</v>
+        <v>45079</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8011,8 +8011,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>22.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8055,7 +8060,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8069,10 +8074,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45315</v>
+        <v>45216</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8085,7 +8090,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8128,7 +8133,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8142,10 +8147,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44732</v>
+        <v>45455</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8159,11 +8164,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>39</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8206,7 +8211,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8216,14 +8221,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45937</v>
+        <v>44732</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8237,11 +8242,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.5</v>
+        <v>39</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8284,7 +8289,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8298,10 +8303,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45664</v>
+        <v>45937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8315,11 +8320,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8372,14 +8377,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45825</v>
+        <v>44475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8393,11 +8398,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>23.7</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45455</v>
+        <v>45825</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8471,11 +8476,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>23.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8518,7 +8523,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45845</v>
+        <v>45730</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8548,7 +8553,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8605,10 +8610,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45034</v>
+        <v>45079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8626,7 +8631,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>20.3</v>
+        <v>7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8669,7 +8674,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8683,10 +8688,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45993</v>
+        <v>45845</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8699,7 +8704,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8742,7 +8747,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8756,10 +8761,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45730</v>
+        <v>45034</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8771,8 +8776,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>7.9</v>
+        <v>20.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8815,7 +8825,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8825,14 +8835,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45999</v>
+        <v>44735</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8844,8 +8854,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>11.3</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8888,7 +8903,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8898,14 +8913,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45999</v>
+        <v>45636</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8917,8 +8932,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8961,7 +8981,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8971,14 +8991,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44473</v>
+        <v>45649</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8990,8 +9010,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9034,7 +9059,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9048,10 +9073,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45079</v>
+        <v>45993</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9063,13 +9088,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9112,7 +9132,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20789-2022</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9126,10 +9146,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44701</v>
+        <v>45999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9142,7 +9162,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>20.3</v>
+        <v>11.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9185,7 +9205,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9195,14 +9215,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45636</v>
+        <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9214,13 +9234,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9280,7 +9295,7 @@
         <v>45079</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9341,7 +9356,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9355,10 +9370,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46104</v>
+        <v>45187</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9370,13 +9385,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>31.7</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9419,7 +9429,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9433,10 +9443,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45281</v>
+        <v>46104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9448,8 +9458,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>13.4</v>
+        <v>31.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9492,7 +9507,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9502,14 +9517,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44735</v>
+        <v>44874</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9521,13 +9536,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9570,7 +9580,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9584,10 +9594,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46139</v>
+        <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9600,7 +9610,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9643,7 +9653,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9657,10 +9667,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46139</v>
+        <v>45315</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9673,7 +9683,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>9.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9716,7 +9726,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9726,14 +9736,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45183</v>
+        <v>45469</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9745,13 +9755,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9794,7 +9799,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45625</v>
+        <v>45463</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9823,8 +9828,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>11.5</v>
+        <v>30.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9867,7 +9877,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9877,14 +9887,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45649</v>
+        <v>46139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9896,13 +9906,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9945,7 +9950,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9959,10 +9964,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45469</v>
+        <v>46139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9975,7 +9980,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10035,7 +10040,7 @@
         <v>45469</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10091,7 +10096,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10101,14 +10106,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44735</v>
+        <v>44741</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10120,13 +10125,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>15.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10169,7 +10169,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44741</v>
+        <v>45625</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>15.6</v>
+        <v>11.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45825</v>
+        <v>45625</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10271,13 +10271,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>25.1</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10320,7 +10315,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10334,10 +10329,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46162</v>
+        <v>45625</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10350,7 +10345,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10393,7 +10388,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10407,10 +10402,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46162</v>
+        <v>45625</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10423,7 +10418,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10466,7 +10461,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 23335-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10480,10 +10475,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44874</v>
+        <v>46162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10496,7 +10491,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10539,7 +10534,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10553,10 +10548,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45463</v>
+        <v>45825</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10574,7 +10569,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>30.7</v>
+        <v>25.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10617,7 +10612,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10631,10 +10626,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45467</v>
+        <v>46162</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10647,7 +10642,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>17.2</v>
+        <v>6.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10690,7 +10685,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10704,10 +10699,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45614</v>
+        <v>45730</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10720,7 +10715,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10763,7 +10758,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10773,14 +10768,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45281</v>
+        <v>44735</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10792,8 +10787,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>43.6</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10853,7 +10853,7 @@
         <v>45468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 53822-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46181</v>
+        <v>45614</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10982,7 +10982,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 26048-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10992,14 +10992,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11011,13 +11011,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>16.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11060,7 +11055,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11070,14 +11065,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45730</v>
+        <v>45183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11089,8 +11084,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28799-2026</t>
+          <t>A 27102-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11143,14 +11143,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11164,11 +11164,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>18</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28804-2026</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46198</v>
+        <v>45281</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11240,13 +11240,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11289,7 +11284,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11303,10 +11298,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46197</v>
+        <v>45281</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11318,13 +11313,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11367,7 +11357,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 28560-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11381,10 +11371,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45530</v>
+        <v>46197</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11396,8 +11386,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11440,7 +11435,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33993-2026</t>
+          <t>A 28799-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11450,14 +11445,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46252</v>
+        <v>46198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11471,11 +11466,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>18</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11518,7 +11513,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27836-2026</t>
+          <t>A 28804-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11528,14 +11523,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11549,11 +11544,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.1</v>
+        <v>11.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11596,7 +11591,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11610,10 +11605,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45153</v>
+        <v>45583</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11625,13 +11620,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>16.9</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11674,7 +11664,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28679-2026</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11684,14 +11674,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46198</v>
+        <v>45250</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11703,13 +11693,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>17.2</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11752,7 +11737,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28787-2026</t>
+          <t>A 27836-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11762,14 +11747,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46198</v>
+        <v>46189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11783,11 +11768,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>13.3</v>
+        <v>0.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11830,7 +11815,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28532-2026</t>
+          <t>A 28787-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11840,14 +11825,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11865,7 +11850,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>13.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11908,7 +11893,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28551-2026</t>
+          <t>A 28532-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11918,14 +11903,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11943,7 +11928,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>22.9</v>
+        <v>4.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11986,7 +11971,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 28679-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12000,10 +11985,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45281</v>
+        <v>46198</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12015,8 +12000,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>17.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12059,7 +12049,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36006-2026</t>
+          <t>A 28551-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12069,14 +12059,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46266</v>
+        <v>46197</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12090,11 +12080,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>22.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12137,7 +12127,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 36006-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12147,14 +12137,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45625</v>
+        <v>46266</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12166,8 +12156,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12210,7 +12205,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 36470-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12224,10 +12219,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45625</v>
+        <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12239,8 +12234,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>13.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12300,7 +12300,7 @@
         <v>46028</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36470-2026</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12370,10 +12370,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46269</v>
+        <v>45621</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12385,13 +12385,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12434,7 +12429,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12448,10 +12443,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45625</v>
+        <v>44701</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12464,7 +12459,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.5</v>
+        <v>20.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12507,7 +12502,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12521,10 +12516,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45625</v>
+        <v>44830</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12536,8 +12531,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12580,7 +12580,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 42274-2022</t>
+          <t>A 39456-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44830</v>
+        <v>46288</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12609,13 +12609,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.5</v>
+        <v>16.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12658,7 +12653,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56276-2021</t>
+          <t>A 38823-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12672,10 +12667,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44479</v>
+        <v>46286</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12687,8 +12682,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>19.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12731,7 +12731,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39456-2026</t>
+          <t>A 20322-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12745,10 +12745,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46288</v>
+        <v>46139</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12804,7 +12804,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38823-2026</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46286</v>
+        <v>44479</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12833,13 +12833,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>9.199999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12882,7 +12877,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20322-2026</t>
+          <t>A 33993-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12892,14 +12887,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46139</v>
+        <v>46252</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12911,8 +12906,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12972,7 +12972,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt ARJEPLOG.xlsx
+++ b/Översikt ARJEPLOG.xlsx
@@ -601,7 +601,7 @@
         <v>45831</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45467</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44552</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>45281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45825</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45189</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45113</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44740</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45891</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44851</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45031-2023</t>
+          <t>A 45030-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3236,7 +3236,7 @@
         <v>45190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3278,21 +3278,144 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Ostticka
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Spindelblomster</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 45031-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>14</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3306,112 +3429,230 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45031-2023 artfynd.xlsx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45031-2023 karta.png", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45031-2023 georefererad karta.tif", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45031-2023 FSC-klagomål.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45031-2023 FSC-klagomål mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45031-2023 tillsynsbegäran.docx", "A 45031-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45031-2023 tillsynsbegäran mail.docx", "A 45031-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45030-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 45417-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>45576</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kortskaftad ärgspik
+Rosenticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1474-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>3.8</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>6</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>9</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>3</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3425,116 +3666,116 @@
 Spindelblomster</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45030-2023 artfynd.xlsx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45030-2023 karta.png", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45030-2023 georefererad karta.tif", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45030-2023 FSC-klagomål.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45030-2023 FSC-klagomål mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45030-2023 tillsynsbegäran.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45030-2023 tillsynsbegäran mail.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45030-2023 prioriterade fågelarter.docx", "A 45030-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 1479-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>4</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>10</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>14</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3548,273 +3789,32 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1479-2026 artfynd.xlsx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1479-2026 karta.png", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1479-2026 georefererad karta.tif", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1479-2026 FSC-klagomål.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1479-2026 FSC-klagomål mail.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1479-2026 tillsynsbegäran.docx", "A 1479-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1479-2026 tillsynsbegäran mail.docx", "A 1479-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1474-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13</v>
-      </c>
-      <c r="U24" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Ostticka
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Ullticka
-Vitgrynig nållav
-Spindelblomster</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1474-2026 artfynd.xlsx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 1474-2026 karta.png", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 1474-2026 georefererad karta.tif", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 1474-2026 FSC-klagomål.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 1474-2026 FSC-klagomål mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 1474-2026 tillsynsbegäran.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 1474-2026 tillsynsbegäran mail.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 1474-2026 prioriterade fågelarter.docx", "A 1474-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 45417-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45576</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>10</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20</v>
-      </c>
-      <c r="U25" t="n">
-        <v>20</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav
-Dvärgbägarlav
-Knottrig blåslav
-Kortskaftad ärgspik
-Rosenticka
-Talltita
-Tretåig hackspett
-Ullticka
-Vedskivlav
-Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45417-2024 artfynd.xlsx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45417-2024 karta.png", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45417-2024 georefererad karta.tif", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45417-2024 FSC-klagomål.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45417-2024 FSC-klagomål mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45417-2024 tillsynsbegäran.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45417-2024 tillsynsbegäran mail.docx", "A 45417-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45417-2024 prioriterade fågelarter.docx", "A 45417-2024")</f>
         <v/>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45327</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28351-2025</t>
+          <t>A 48673-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45818</v>
+        <v>45203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.4</v>
+        <v>32.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4111,18 +4111,255 @@
         <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
       </c>
       <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gränsticka
+Hökuggla
+Harticka
+Lunglav
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 45032-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" t="n">
+        <v>7</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Vitskaftad svartspik
+Gammelgransskål
+Harticka
+Knottrig blåslav
+Tretåig hackspett
+Vedtrappmossa
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 28351-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="n">
         <v>13</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U30" t="n">
         <v>13</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4134,112 +4371,112 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 28351-2025 artfynd.xlsx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 28351-2025 karta.png", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 28351-2025 georefererad karta.tif", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 28351-2025 FSC-klagomål.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 28351-2025 FSC-klagomål mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 28351-2025 tillsynsbegäran.docx", "A 28351-2025")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 28351-2025 tillsynsbegäran mail.docx", "A 28351-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 45032-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 1478-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>45190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="D31" s="1" t="n">
+        <v>46033</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Vitskaftad svartspik
@@ -4251,243 +4488,6 @@
 Vitgrynig nållav</t>
         </is>
       </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45032-2023 artfynd.xlsx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45032-2023 karta.png", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45032-2023 georefererad karta.tif", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45032-2023 FSC-klagomål.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45032-2023 FSC-klagomål mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45032-2023 tillsynsbegäran.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45032-2023 tillsynsbegäran mail.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45032-2023 prioriterade fågelarter.docx", "A 45032-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 48673-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45203</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Gränsticka
-Hökuggla
-Harticka
-Lunglav
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 48673-2023 artfynd.xlsx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 48673-2023 karta.png", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 48673-2023 georefererad karta.tif", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 48673-2023 FSC-klagomål.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 48673-2023 FSC-klagomål mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 48673-2023 tillsynsbegäran.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 48673-2023 tillsynsbegäran mail.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 48673-2023 prioriterade fågelarter.docx", "A 48673-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1478-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Vitskaftad svartspik
-Gammelgransskål
-Harticka
-Knottrig blåslav
-Tretåig hackspett
-Vedtrappmossa
-Vitgrynig nållav</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 1478-2026 artfynd.xlsx", "A 1478-2026")</f>
         <v/>
@@ -4541,7 +4541,7 @@
         <v>45937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 25229-2023</t>
+          <t>A 59199-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45079</v>
+        <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4668,16 +4668,11 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4707,12 +4702,126 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
+        <v>9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Gammelgransskål
+Rosenticka
+Rynkskinn
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 25229-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Gammelgransskål
@@ -4721,152 +4830,43 @@
 Tretåig hackspett</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 25229-2023 artfynd.xlsx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 25229-2023 karta.png", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 25229-2023 georefererad karta.tif", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 25229-2023 FSC-klagomål.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 25229-2023 FSC-klagomål mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 25229-2023 tillsynsbegäran.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 25229-2023 tillsynsbegäran mail.docx", "A 25229-2023")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 25229-2023 prioriterade fågelarter.docx", "A 25229-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 59199-2021</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>44490</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>9</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Gammelgransskål
-Rosenticka
-Rynkskinn
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 59199-2021 artfynd.xlsx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 59199-2021 karta.png", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 59199-2021 georefererad karta.tif", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 59199-2021 FSC-klagomål.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 59199-2021 FSC-klagomål mail.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 59199-2021 tillsynsbegäran.docx", "A 59199-2021")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 59199-2021 tillsynsbegäran mail.docx", "A 59199-2021")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12403-2025</t>
+          <t>A 64803-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45730</v>
+        <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>43</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4923,18 +4923,126 @@
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
       </c>
       <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Gullmurkling
+Lunglav
+Rosenticka
+Ullticka</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 12403-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45730</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="n">
         <v>9</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>9</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -4942,151 +5050,43 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 12403-2025 artfynd.xlsx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 12403-2025 karta.png", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 12403-2025 georefererad karta.tif", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 12403-2025 FSC-klagomål.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 12403-2025 FSC-klagomål mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 12403-2025 tillsynsbegäran.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 12403-2025 tillsynsbegäran mail.docx", "A 12403-2025")</f>
         <v/>
       </c>
-      <c r="AE35">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 12403-2025 prioriterade fågelarter.docx", "A 12403-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 64803-2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>43</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Gullmurkling
-Lunglav
-Rosenticka
-Ullticka</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 64803-2023 artfynd.xlsx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 64803-2023 karta.png", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 64803-2023 georefererad karta.tif", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 64803-2023 FSC-klagomål.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 64803-2023 FSC-klagomål mail.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 64803-2023 tillsynsbegäran.docx", "A 64803-2023")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 64803-2023 tillsynsbegäran mail.docx", "A 64803-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26143-2024</t>
+          <t>A 10525-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45467</v>
+        <v>45366</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>15.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5149,262 +5149,262 @@
         <v>3</v>
       </c>
       <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Spindelblomster
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 26143-2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="U37" t="n">
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Knottrig blåslav
 Vedticka</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 26143-2024 artfynd.xlsx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 26143-2024 karta.png", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 26143-2024 georefererad karta.tif", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 26143-2024 FSC-klagomål.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 26143-2024 FSC-klagomål mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 26143-2024 tillsynsbegäran.docx", "A 26143-2024")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 26143-2024 tillsynsbegäran mail.docx", "A 26143-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 15171-2022</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>44658</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+      <c r="E39" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>48</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>2</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>3</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>3</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>1</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Tretåig hackspett
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 15171-2022 artfynd.xlsx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 15171-2022 karta.png", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 15171-2022 georefererad karta.tif", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 15171-2022 FSC-klagomål.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 15171-2022 FSC-klagomål mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 15171-2022 tillsynsbegäran.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 15171-2022 tillsynsbegäran mail.docx", "A 15171-2022")</f>
         <v/>
       </c>
-      <c r="AE38">
+      <c r="AE39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 15171-2022 prioriterade fågelarter.docx", "A 15171-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A 10525-2024</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>45366</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Spindelblomster
-Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10525-2024 artfynd.xlsx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10525-2024 karta.png", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10525-2024 georefererad karta.tif", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10525-2024 FSC-klagomål.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10525-2024 FSC-klagomål mail.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10525-2024 tillsynsbegäran.docx", "A 10525-2024")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10525-2024 tillsynsbegäran mail.docx", "A 10525-2024")</f>
         <v/>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45324-2022</t>
+          <t>A 41375-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44841</v>
+        <v>45559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5552,20 +5552,25 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>23.2</v>
+        <v>5.9</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5577,167 +5582,162 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Brudsporre</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 45324-2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>44841</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Bergand
 Sångsvan</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 45324-2022 artfynd.xlsx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 45324-2022 karta.png", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 45324-2022 georefererad karta.tif", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 45324-2022 FSC-klagomål.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 45324-2022 FSC-klagomål mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 45324-2022 tillsynsbegäran.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 45324-2022 tillsynsbegäran mail.docx", "A 45324-2022")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2506/fåglar/A 45324-2022 prioriterade fågelarter.docx", "A 45324-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 41375-2024</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>45559</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ARJEPLOG</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot
-Brudsporre</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 41375-2024 artfynd.xlsx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 41375-2024 karta.png", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 41375-2024 georefererad karta.tif", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 41375-2024 FSC-klagomål.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 41375-2024 FSC-klagomål mail.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 41375-2024 tillsynsbegäran.docx", "A 41375-2024")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 41375-2024 tillsynsbegäran mail.docx", "A 41375-2024")</f>
         <v/>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         <v>44642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10476-2026</t>
+          <t>A 20905-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>45777</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6103,31 +6103,31 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>10.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6139,46 +6139,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20905-2025</t>
+          <t>A 10476-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.6</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6244,39 +6244,39 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 20905-2025 artfynd.xlsx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/artfynd/A 10476-2026 artfynd.xlsx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 20905-2025 karta.png", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor/A 10476-2026 karta.png", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 20905-2025 georefererad karta.tif", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/kartor_geotiff/A 10476-2026 georefererad karta.tif", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 20905-2025 FSC-klagomål.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomål/A 10476-2026 FSC-klagomål.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 20905-2025 FSC-klagomål mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/klagomålsmail/A 10476-2026 FSC-klagomål mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 20905-2025 tillsynsbegäran.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsyn/A 10476-2026 tillsynsbegäran.docx", "A 10476-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 20905-2025 tillsynsbegäran mail.docx", "A 20905-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2506/tillsynsmail/A 10476-2026 tillsynsbegäran mail.docx", "A 10476-2026")</f>
         <v/>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
         <v>44520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44479</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44479</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44479</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44751-2022</t>
+          <t>A 56278-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44840</v>
+        <v>44479</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6604,13 +6604,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>26.1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6653,7 +6648,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56278-2021</t>
+          <t>A 19620-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6663,14 +6658,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44479</v>
+        <v>44694</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6680,6 +6675,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>ARJEPLOG</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -6726,7 +6726,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52573-2022</t>
+          <t>A 72279-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6736,14 +6736,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44874</v>
+        <v>44543</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.7</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19620-2022</t>
+          <t>A 44751-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44694</v>
+        <v>44840</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6830,11 +6830,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>26.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72279-2021</t>
+          <t>A 52573-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6887,14 +6887,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44543</v>
+        <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56785-2024</t>
+          <t>A 23949-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45625</v>
+        <v>45455</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7052,8 +7052,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>11.2</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7096,7 +7101,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55124-2024</t>
+          <t>A 26811-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7106,14 +7111,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45618</v>
+        <v>44735</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,8 +7130,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>18.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7169,7 +7179,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26103-2024</t>
+          <t>A 64840-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7183,10 +7193,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45467</v>
+        <v>45281</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7199,7 +7209,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -7242,7 +7252,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35627-2025</t>
+          <t>A 56785-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7256,10 +7266,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45859</v>
+        <v>45625</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7272,7 +7282,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7315,7 +7325,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35194-2024</t>
+          <t>A 56800-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7329,10 +7339,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45530</v>
+        <v>45625</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7345,7 +7355,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>20.1</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7388,7 +7398,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42331-2025</t>
+          <t>A 54589-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7402,10 +7412,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45903</v>
+        <v>44473</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7418,7 +7428,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7461,7 +7471,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42597-2025</t>
+          <t>A 52581-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7475,10 +7485,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45905</v>
+        <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7491,7 +7501,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7534,7 +7544,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 25440-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7548,10 +7558,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44833</v>
+        <v>45463</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7563,8 +7573,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>24.6</v>
+        <v>30.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7607,7 +7622,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 526-2025</t>
+          <t>A 46910-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7617,14 +7632,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45664</v>
+        <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7636,13 +7651,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7685,7 +7695,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43045-2022</t>
+          <t>A 55266-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7699,10 +7709,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44833</v>
+        <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7715,7 +7725,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>23.2</v>
+        <v>11.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7758,7 +7768,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64832-2023</t>
+          <t>A 55124-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7772,10 +7782,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45281</v>
+        <v>45618</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7788,7 +7798,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>43.6</v>
+        <v>18.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7831,7 +7841,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36623-2023</t>
+          <t>A 55422-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7841,14 +7851,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45153</v>
+        <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7866,7 +7876,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>16.9</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7909,7 +7919,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31104-2025</t>
+          <t>A 56794-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7923,10 +7933,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45832</v>
+        <v>45625</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7939,7 +7949,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7982,7 +7992,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25275-2023</t>
+          <t>A 20789-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7996,10 +8006,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45079</v>
+        <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8011,13 +8021,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>22.7</v>
+        <v>20.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8060,7 +8065,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50255-2023</t>
+          <t>A 26103-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8074,10 +8079,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45216</v>
+        <v>45467</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8090,7 +8095,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8133,7 +8138,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23949-2024</t>
+          <t>A 56782-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8147,10 +8152,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45455</v>
+        <v>45625</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8162,13 +8167,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25559-2022</t>
+          <t>A 42274-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44732</v>
+        <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8242,11 +8242,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>39</v>
+        <v>6.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48987-2025</t>
+          <t>A 64832-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8299,14 +8299,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45937</v>
+        <v>45281</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8318,13 +8318,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.5</v>
+        <v>43.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8367,7 +8362,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55422-2021</t>
+          <t>A 56276-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8381,10 +8376,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44475</v>
+        <v>44479</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8396,13 +8391,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>19.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8445,7 +8435,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29662-2025</t>
+          <t>A 45072-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45825</v>
+        <v>45187</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8474,13 +8464,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>23.7</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8523,7 +8508,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12447-2025</t>
+          <t>A 12409-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8540,7 +8525,7 @@
         <v>45730</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8553,7 +8538,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8596,7 +8581,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25239-2023</t>
+          <t>A 64816-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8610,10 +8595,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45079</v>
+        <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8625,13 +8610,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>13.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8674,7 +8654,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34426-2025</t>
+          <t>A 28354-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8684,14 +8664,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45845</v>
+        <v>44735</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8703,8 +8683,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8747,7 +8732,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17536-2023</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8761,10 +8746,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45034</v>
+        <v>44833</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8776,13 +8761,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>20.3</v>
+        <v>24.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8825,7 +8805,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28354-2022</t>
+          <t>A 43045-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8835,14 +8815,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44735</v>
+        <v>44833</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8854,13 +8834,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>23.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8903,7 +8878,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58989-2024</t>
+          <t>A 58370-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8913,14 +8888,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45636</v>
+        <v>45250</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8932,13 +8907,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8981,7 +8951,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61729-2024</t>
+          <t>A 35194-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8991,14 +8961,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45649</v>
+        <v>45530</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9010,13 +8980,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>20.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9059,7 +9024,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59887-2025</t>
+          <t>A 25275-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9073,10 +9038,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45993</v>
+        <v>45079</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9088,8 +9053,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>22.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9132,7 +9102,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60767-2025</t>
+          <t>A 31104-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9146,10 +9116,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45999</v>
+        <v>45832</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9162,7 +9132,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9205,7 +9175,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60766-2025</t>
+          <t>A 36623-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9219,10 +9189,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45999</v>
+        <v>45153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9234,8 +9204,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>16.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9278,7 +9253,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25270-2023</t>
+          <t>A 44218-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9288,14 +9263,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45079</v>
+        <v>45183</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9309,11 +9284,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9356,7 +9331,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45072-2023</t>
+          <t>A 3006-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9370,10 +9345,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45187</v>
+        <v>45315</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9386,7 +9361,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9429,7 +9404,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14861-2026</t>
+          <t>A 25559-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9443,10 +9418,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46104</v>
+        <v>44732</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9460,11 +9435,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>31.7</v>
+        <v>39</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9507,7 +9482,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52581-2022</t>
+          <t>A 56754-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9521,10 +9496,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44874</v>
+        <v>45625</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9537,7 +9512,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9580,7 +9555,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54589-2021</t>
+          <t>A 29662-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9594,10 +9569,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44473</v>
+        <v>45825</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9609,8 +9584,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>23.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9653,7 +9633,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3006-2024</t>
+          <t>A 61729-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9663,14 +9643,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45315</v>
+        <v>45649</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9682,8 +9662,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>9.1</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9726,7 +9711,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26486-2024</t>
+          <t>A 526-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9736,14 +9721,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45469</v>
+        <v>45664</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9755,8 +9740,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9799,7 +9789,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25440-2024</t>
+          <t>A 48987-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9809,14 +9799,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45463</v>
+        <v>45937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9830,11 +9820,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>30.7</v>
+        <v>6.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9877,7 +9867,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20319-2026</t>
+          <t>A 35627-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9891,10 +9881,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46139</v>
+        <v>45859</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9907,7 +9897,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9950,7 +9940,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20326-2026</t>
+          <t>A 42331-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9964,10 +9954,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46139</v>
+        <v>45903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9980,7 +9970,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10023,7 +10013,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26472-2024</t>
+          <t>A 42597-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10037,10 +10027,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45469</v>
+        <v>45905</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10053,7 +10043,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10096,7 +10086,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 27092-2022</t>
+          <t>A 50255-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10110,10 +10100,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44741</v>
+        <v>45216</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10126,7 +10116,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10169,7 +10159,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56754-2024</t>
+          <t>A 34426-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10183,10 +10173,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45625</v>
+        <v>45845</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10199,7 +10189,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10242,7 +10232,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56800-2024</t>
+          <t>A 17536-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10256,10 +10246,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45625</v>
+        <v>45034</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10271,8 +10261,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>20.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10315,7 +10310,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56782-2024</t>
+          <t>A 59887-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10329,10 +10324,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45625</v>
+        <v>45993</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10345,7 +10340,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10388,7 +10383,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56794-2024</t>
+          <t>A 60767-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10402,10 +10397,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45625</v>
+        <v>45999</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10418,7 +10413,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10461,7 +10456,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23335-2026</t>
+          <t>A 60766-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10475,10 +10470,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46162</v>
+        <v>45999</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10491,7 +10486,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10534,7 +10529,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29674-2025</t>
+          <t>A 12447-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10548,10 +10543,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45825</v>
+        <v>45730</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10563,13 +10558,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>25.1</v>
+        <v>7.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10612,7 +10602,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23330-2026</t>
+          <t>A 25239-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10626,10 +10616,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46162</v>
+        <v>45079</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10641,8 +10631,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10685,7 +10680,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 12409-2025</t>
+          <t>A 58989-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10695,14 +10690,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45730</v>
+        <v>45636</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10714,8 +10709,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10758,7 +10758,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26811-2022</t>
+          <t>A 25270-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10768,14 +10768,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44735</v>
+        <v>45079</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>29</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10836,7 +10836,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26479-2024</t>
+          <t>A 14861-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10850,10 +10850,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45468</v>
+        <v>46104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10865,8 +10865,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>6.9</v>
+        <v>31.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10909,7 +10914,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53822-2024</t>
+          <t>A 20319-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10923,10 +10928,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45614</v>
+        <v>46139</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10939,7 +10944,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10982,7 +10987,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26048-2026</t>
+          <t>A 20326-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10996,10 +11001,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46181</v>
+        <v>46139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11012,7 +11017,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>16.9</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11055,7 +11060,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44218-2023</t>
+          <t>A 26486-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11065,14 +11070,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45183</v>
+        <v>45469</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11084,13 +11089,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27102-2026</t>
+          <t>A 26472-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11143,14 +11143,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46188</v>
+        <v>45469</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11162,13 +11162,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11211,7 +11206,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64840-2023</t>
+          <t>A 27092-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11225,10 +11220,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45281</v>
+        <v>44741</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11241,7 +11236,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>15.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11284,7 +11279,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64816-2023</t>
+          <t>A 29674-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11298,10 +11293,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45281</v>
+        <v>45825</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11313,8 +11308,13 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>13.4</v>
+        <v>25.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11357,7 +11357,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28560-2026</t>
+          <t>A 23330-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46197</v>
+        <v>46162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11386,13 +11386,8 @@
           <t>ARJEPLOG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
- 